--- a/output/messaging_matrix.xlsx
+++ b/output/messaging_matrix.xlsx
@@ -7,8 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Messaging Matrix" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Tagged Ads" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Findings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Messaging Matrix" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Audience Matrix" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Proof Points" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Tagged Ads" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +39,20 @@
     <font>
       <i val="1"/>
       <color rgb="00666666"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C55A11"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="5">
@@ -87,8 +104,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -96,15 +124,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -115,7 +143,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -482,10 +510,233 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>THE FINDING</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>All three players are fighting over the same "one platform, less busywork" consolidation pitch aimed at SMBs and project managers, leaving enterprise security and customer support completely unclaimed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>WHITESPACE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>The opportunity</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Enterprise-grade security, governance and compliance — paired with real human support. Zero ads in the set touch either theme. Asana gestures at enterprise credibility with its Fortune 100 stat, but never actually sells admin controls, data residency, SSO, permissions or audit trails, and no one sells implementation help, onboarding, or a named support contact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="45" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Consolidation buyers are being asked to move docs, chat, tasks and goals into one system of record — which raises the exact objections nobody is answering: who can see what, where does the data live, will IT approve it, and who helps us migrate. Those objections are what kill deals above 200 seats, and they're also where deal sizes and retention live. Every competitor is competing on free trials and self-serve signup, which caps them at low-ACV SMB and pushes the category toward price wars. An enterprise-and-support message is both uncontested and pointed at the highest-value segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="45" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Recommended move</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Launch a dedicated campaign line built on trust infrastructure, not features: SOC 2 / ISO, granular permissions, SSO/SCIM, audit logs, data residency, plus a guaranteed onboarding and named support commitment (e.g. "live human in under an hour," "dedicated migration team"). Target IT, security and ops leaders at 200+ seat companies with a security-review-ready one-pager as the CTA instead of "start free." Keep the self-serve free-trial track running separately for SMB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>HOW EACH BRAND IS POSITIONED</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Asana</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Clarity and accountability — who is doing what by when, with automation to cut busywork.
+Targets: Operations and project managers exclusively (3 of 3 ads); the only brand not chasing SMB.
+Signature proof: 85% of the Fortune 100 trust Asana.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>ClickUp</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>The everything app — replace and consolidate your whole tool stack, cheaply.
+Targets: Small business and a broad general audience; the only brand leading on price/value.
+Signature proof: Save a day every week; trusted by 2 million teams.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Monday.com</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>The flexible, no-code Work OS that adapts to any workflow across any department.
+Targets: Small business primarily, with some ops/PM crossover.
+Signature proof: 225,000+ teams trust monday.com.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>PROOF POINTS THE CATEGORY LEANS ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Customer-count and logo-volume claims used as social proof (2 million teams, 225,000+ teams, 85% of the Fortune 100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Time-saved quantification ("save a day every week," "automate the busywork")</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Tool-consolidation math ("does the work of ten apps," "cut your tool stack in half," "one place")</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Zero-risk entry offers as the standard CTA (free forever, start free, 30-day free trial)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Anti-spreadsheet / anti-manual-work framing as the implied status quo enemy</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>RECOMMENDATIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>1.</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Own the enterprise trust lane with a security-and-governance campaign targeted at IT and security buyers, gated on a compliance pack rather than a free trial.
+Why: It is the single largest gap in the matrix and it points at the segment with the highest ACV and lowest churn. Competing head-on for SMB free signups means fighting ClickUp's price message and Monday's brand spend with no differentiation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="48" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Make human support a headline claim with a specific, falsifiable commitment — a response-time SLA, a named onboarding lead, or a migration-done-for-you offer.
+Why: Every competitor sells consolidation but none address the cost and risk of actually consolidating. Support is unclaimed, cheap to prove, and directly de-risks the biggest objection to switching platforms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="48" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Replace generic customer-count claims with outcome proof tied to a named segment — a specific customer, a specific number, a specific timeframe.
+Why: "X teams trust us" is now category wallpaper and a volume contest ClickUp wins at 2 million. Only ClickUp uses an outcome stat, and it's vague. Concrete, attributed results cut through a field of interchangeable trust badges.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="48" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>4.</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Cede the "all-in-one" framing and reposition against consolidation fatigue — depth and reliability in the workflows that actually matter, rather than replacing ten apps.
+Why: Integrations/all-in-one is the most crowded theme in the matrix (7 ads across 3 brands). Buyers who have already tried and abandoned an everything-app are an addressable, resentful audience no one is speaking to.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -497,168 +748,162 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Competitor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Price / Value</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Speed / Efficiency</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Ease of Use</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Integrations / All-in-one</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Trust / Scale</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>Customer Support</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>Enterprise / Security</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>Innovation / AI</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Asana</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="9" t="n"/>
+      <c r="C2" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="D2" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="E2" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="F2" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="G2" s="11" t="n"/>
+      <c r="H2" s="11" t="n"/>
+      <c r="I2" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n"/>
-      <c r="I2" s="6" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>ClickUp</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="9" t="n"/>
+      <c r="E3" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="11" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="9" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Monday.com</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="6" t="n"/>
-      <c r="E3" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-      <c r="I3" s="6" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Monday.com</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="4" t="n">
+      <c r="E4" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="F4" s="9" t="n"/>
+      <c r="G4" s="11" t="n"/>
+      <c r="H4" s="11" t="n"/>
+      <c r="I4" s="9" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="12">
         <f>SUM(B2:B4)</f>
         <v/>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="12">
         <f>SUM(C2:C4)</f>
         <v/>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="12">
         <f>SUM(D2:D4)</f>
         <v/>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="12">
         <f>SUM(E2:E4)</f>
         <v/>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="12">
         <f>SUM(F2:F4)</f>
         <v/>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="13">
         <f>SUM(G2:G4)</f>
         <v/>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="13">
         <f>SUM(H2:H4)</f>
         <v/>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="12">
         <f>SUM(I2:I4)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Cell = number of that brand's ads using the theme. Blue = a theme in play. Peach columns = whitespace (no competitor is using it).</t>
         </is>
@@ -669,7 +914,272 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Competitor</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Small business</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Enterprise / IT</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Marketing teams</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Sales teams</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Developers / Technical</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>Operations / Project managers</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Executives / Leadership</t>
+        </is>
+      </c>
+      <c r="I1" s="6" t="inlineStr">
+        <is>
+          <t>General / Everyone</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Asana</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="n"/>
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="11" t="n"/>
+      <c r="G2" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" s="11" t="n"/>
+      <c r="I2" s="9" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>ClickUp</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="11" t="n"/>
+      <c r="G3" s="9" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Monday.com</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="11" t="n"/>
+      <c r="G4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="11" t="n"/>
+      <c r="I4" s="9" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B5" s="12">
+        <f>SUM(B2:B4)</f>
+        <v/>
+      </c>
+      <c r="C5" s="13">
+        <f>SUM(C2:C4)</f>
+        <v/>
+      </c>
+      <c r="D5" s="13">
+        <f>SUM(D2:D4)</f>
+        <v/>
+      </c>
+      <c r="E5" s="13">
+        <f>SUM(E2:E4)</f>
+        <v/>
+      </c>
+      <c r="F5" s="13">
+        <f>SUM(F2:F4)</f>
+        <v/>
+      </c>
+      <c r="G5" s="12">
+        <f>SUM(G2:G4)</f>
+        <v/>
+      </c>
+      <c r="H5" s="13">
+        <f>SUM(H2:H4)</f>
+        <v/>
+      </c>
+      <c r="I5" s="12">
+        <f>SUM(I2:I4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Cell = number of that brand's ads aimed at the audience. Peach columns = audiences no competitor is speaking to.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Competitor</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Proof point cited</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Times used</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Asana</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>85% of the Fortune 100 trust Asana</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>ClickUp</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>Save a day every week</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr"/>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Trusted by 2 million teams</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Monday.com</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>225,000+ teams trust monday.com</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -681,365 +1191,357 @@
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Competitor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Ad copy</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Themes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Audience</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Proof points</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Format</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>First seen</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Asana</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>Manage your team's work in one place. Asana keeps projects on track with timelines, automation, and clear ownership. Start free.</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
-        <is>
-          <t>Speed / Efficiency, Ease of Use, Integrations / All-in-one, Price / Value</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>Team managers and project leaders</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr"/>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>Ease of Use, Integrations / All-in-one</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>Operations / Project managers</t>
+        </is>
+      </c>
+      <c r="E2" s="15" t="inlineStr"/>
+      <c r="F2" s="15" t="inlineStr">
         <is>
           <t>Search</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="15" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Asana</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Less busywork, more impact. Automate routine tasks and hit every deadline. Trusted by 85% of the Fortune 100.</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>Speed / Efficiency, Trust / Scale</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>Enterprise/Large organizations</t>
-        </is>
-      </c>
-      <c r="E3" s="10" t="inlineStr">
-        <is>
-          <t>85% of the Fortune 100</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>Speed / Efficiency, Ease of Use, Trust / Scale, Innovation / AI</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>Operations / Project managers</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>85% of the Fortune 100 trust Asana</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
         <is>
           <t>Search</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="15" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Asana</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>See who is doing what by when. Every project gets a clear owner and due date. Try Asana free for 30 days.</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>Speed / Efficiency, Ease of Use</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>Project managers and team leads</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>30-day free trial</t>
-        </is>
-      </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Ease of Use, Integrations / All-in-one</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>Operations / Project managers</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr"/>
+      <c r="F4" s="15" t="inlineStr">
         <is>
           <t>Display</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Monday.com</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>The Work OS that adapts to you. Build any workflow, no code required. Get started free.</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>Price / Value, Speed / Efficiency, Ease of Use, Innovation / AI</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>Small to mid-market businesses and teams seeking flexible workflow solutions without technical expertise</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr"/>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Ease of Use, Integrations / All-in-one</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Small business</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr"/>
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>Search</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="15" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Monday.com</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Ditch the spreadsheets. Manage projects, sales, and marketing on one colorful platform. 225,000+ teams trust monday.com.</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>Ease of Use, Integrations / All-in-one, Trust / Scale</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>Project, sales, and marketing teams/managers</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Ease of Use, Integrations / All-in-one</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Small business</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>225,000+ teams trust monday.com</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>Display</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Monday.com</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>Automate the busywork. Set it once and let monday.com handle the follow-ups. Start your free trial.</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>Speed / Efficiency, Ease of Use</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>Busy professionals and team leaders seeking to reduce manual work</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr"/>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Speed / Efficiency</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Operations / Project managers</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr"/>
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>Search</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>ClickUp</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>One app to replace them all. Docs, tasks, goals, and chat in one place. Save a day every week. Free forever.</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>Price / Value, Speed / Efficiency, Integrations / All-in-one</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>Teams and individuals seeking to consolidate their productivity tools and save time</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>Save a day every week, Free forever</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Integrations / All-in-one, Speed / Efficiency, Price / Value</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Small business</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>Save a day every week</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t>Search</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>ClickUp</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>The everything app for work. Bring your team's tools together. Trusted by 2 million teams.</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>Integrations / All-in-one, Trust / Scale</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>Teams and team leaders looking to consolidate their work tools</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>2 million teams</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>General / Everyone</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>Trusted by 2 million teams</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>Display</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>ClickUp</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>Cut your tool stack in half. ClickUp does the work of ten apps. Get started free.</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>Price / Value, Speed / Efficiency, Integrations / All-in-one</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>Teams and businesses using multiple disparate tools looking to consolidate their software stack</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>does the work of ten apps</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Integrations / All-in-one, Price / Value</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>Small business</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr"/>
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>Search</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="15" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>

--- a/output/messaging_matrix.xlsx
+++ b/output/messaging_matrix.xlsx
@@ -55,7 +55,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -70,11 +70,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -104,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -120,9 +115,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -132,13 +124,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -510,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -525,7 +511,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>All three players are fighting over the same "one platform, less busywork" consolidation pitch aimed at SMBs and project managers, leaving enterprise security and customer support completely unclaimed.</t>
+          <t>Every brand is shouting some mix of performance, comfort and style, while the two claims that actually build defensible preference — community/belonging and sustainability — are being run by only three brands each, and almost nobody is backing claims with hard, specific proof.</t>
         </is>
       </c>
     </row>
@@ -544,7 +530,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Enterprise-grade security, governance and compliance — paired with real human support. Zero ads in the set touch either theme. Asana gestures at enterprise credibility with its Fortune 100 stat, but never actually sells admin controls, data residency, SSO, permissions or audit trails, and no one sells implementation help, onboarding, or a named support contact.</t>
+          <t>Community and belonging is the least crowded theme in the set: only Gymshark (2 ads) and Fabletics (1 ad) use it, and Gymshark owns it purely for the gym-bro/Gen Z lifter. Sustainability is equally thin (Arc'teryx, Fabletics, lululemon, Patagonia — one ad each) and, apart from Patagonia, is treated as a throwaway line rather than a campaign. That leaves a wide-open lane: identity and belonging attached to a specific training tribe outside the weight room — and, secondarily, credible, specific durability/sustainability proof instead of vague 'eco' language.</t>
         </is>
       </c>
     </row>
@@ -556,7 +542,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Consolidation buyers are being asked to move docs, chat, tasks and goals into one system of record — which raises the exact objections nobody is answering: who can see what, where does the data live, will IT approve it, and who helps us migrate. Those objections are what kill deals above 200 seats, and they're also where deal sizes and retention live. Every competitor is competing on free trials and self-serve signup, which caps them at low-ACV SMB and pushes the category toward price wars. An enterprise-and-support message is both uncontested and pointed at the highest-value segment.</t>
+          <t>Performance and comfort claims are commoditised — 11 of 12 brands claim performance, 9 claim comfort, and the copy is near-interchangeable ('breathable', 'buttery-soft', 'built to move'). Claims everyone makes get arbitrated on price, which is why Fabletics and Under Armour are already discounting to 50-80% off. Belonging and proven durability are the only two angles in this matrix that raise willingness to pay, drive repeat purchase and lower acquisition cost through word-of-mouth rather than promo depth.</t>
         </is>
       </c>
     </row>
@@ -568,7 +554,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Launch a dedicated campaign line built on trust infrastructure, not features: SOC 2 / ISO, granular permissions, SSO/SCIM, audit logs, data residency, plus a guaranteed onboarding and named support commitment (e.g. "live human in under an hour," "dedicated migration team"). Target IT, security and ops leaders at 200+ seat companies with a security-review-ready one-pager as the CTA instead of "start free." Keep the self-serve free-trial track running separately for SMB.</t>
+          <t>Build one owned community platform tied to a named audience the category under-serves — size-inclusive lifters, yoga/studio (only Alo and lululemon touch it, one ad each), or the everyday runner who is neither an elite Tracksmith type nor a Nike marathoner. Ship it as a recurring, dated program (weekly run/lift meetups, a members' club, a challenge series with named cohorts), then make the community itself the proof point in ads: member counts, cities, sessions completed. Pair it with one hard durability guarantee in Patagonia's style ('Built for years, not seasons') so the belonging story has a product spine and does not need discounts to convert.</t>
         </is>
       </c>
     </row>
@@ -582,143 +568,263 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Asana</t>
+          <t>Alo Yoga</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Clarity and accountability — who is doing what by when, with automation to cut busywork.
-Targets: Operations and project managers exclusively (3 of 3 ads); the only brand not chasing SMB.
-Signature proof: 85% of the Fortune 100 trust Asana.</t>
+          <t>Studio-to-street fashion activewear sold on softness and celebrity-adjacent style rather than technical performance — the only brand here not leading with performance.
+Targets: Everyday athleisure wearers and yoga/studio, split across women and men
+Signature proof: 4.5 rating from 21,131 reviews — by far the largest review volume in the set</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>ClickUp</t>
+          <t>Arc'teryx</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>The everything app — replace and consolidate your whole tool stack, cheaply.
-Targets: Small business and a broad general audience; the only brand leading on price/value.
-Signature proof: Save a day every week; trusted by 2 million teams.</t>
+          <t>Technical mountain performance: lightweight, breathable, sun- and weather-protective gear for long days on the trail.
+Targets: Outdoor and hiking, heavily (4 of 6 ads)
+Signature proof: High-performance apparel claim plus free shipping and returns; review proof is thin (4.0 from 24)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Monday.com</t>
+          <t>Fabletics</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>The flexible, no-code Work OS that adapts to any workflow across any department.
-Targets: Small business primarily, with some ops/PM crossover.
-Signature proof: 225,000+ teams trust monday.com.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+          <t>Price-led activewear for everyone — 'stop overpaying' — extended into scrubs and swim, with size inclusivity as its distinguishing angle.
+Targets: Women, size-inclusive shoppers, plus men and workwear (scrubs) buyers
+Signature proof: $15 first set / 80% off as a new VIP — the deepest offer in the category</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Gymshark</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>The gym is the identity: workout clothes plus culture and community for people who train.
+Targets: Gym and strength trainers, Gen Z men and women, everyday wear
+Signature proof: Free Returns plus editorial/community content ('However you gym, we've got the clothes and community')</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>New Balance</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Heritage craftsmanship meets everyday comfort — lifestyle footwear first, running technology second.
+Targets: Everyday athleisure (3 of 5 ads), runners, men, back-to-school families
+Signature proof: Established in 1906, New Infinion Foam midsole, Extended Widths — the most product-specific proof stack in the set</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>The default full-range athletic store: performance and comfort across every sport, sold on breadth and service.
+Targets: Women, runners, everyday wearers; broad by design
+Signature proof: 4.7 rating from 6,660 reviews plus 1-3 day average delivery and live support</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Swiss-engineered running innovation — maximum cushioning and element-proof tech, the most innovation-forward brand here.
+Targets: Runners above all (3 of 6 ads), with light gym and outdoor extension
+Signature proof: Maximum cushioning, free shipping and 30-day returns; LightSpray upper as a proprietary technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Patagonia</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Buy-it-for-life outdoor gear with environmental purpose — 'built for years, not seasons'.
+Targets: Outdoor and hiking exclusively
+Signature proof: Guaranteed Quality / Made to Last, plus profits to the planet</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Tracksmith</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Boston-designed apparel for serious runners in pursuit of personal excellence — craft and heritage over cushioning tech.
+Targets: Runners, near-exclusively (4 of 6 ads)
+Signature proof: 5.0 rating from 22 reviews and 'Designed in Boston to meet the rigorous demands of runners'</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Under Armour</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Performance cushioning and durability, currently sold primarily on discount depth.
+Targets: Runners and general training, women and men, everyday
+Signature proof: 30-50% off sitewide and 4.7 rating from 305 reviews</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Vuori</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Performance apparel reframed as lifestyle style — 'built to move in, styled for life' — the broadest claim set of any brand here.
+Targets: The widest audience spread: women, men, gym, outdoor and everyday athleisure
+Signature proof: None cited — relies on free shipping over $75 and brand language alone</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>lululemon</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Comfort and versatility for the do-it-all wardrobe — one piece to run, train, flow and relax in.
+Targets: Women and everyday athleisure primarily, with yoga, gym and running extensions
+Signature proof: None cited — sells on functional descriptors (sweat-wicking, breathable, anti-stink)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>PROOF POINTS THE CATEGORY LEANS ON</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Customer-count and logo-volume claims used as social proof (2 million teams, 225,000+ teams, 85% of the Fortune 100)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Time-saved quantification ("save a day every week," "automate the busywork")</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Tool-consolidation math ("does the work of ten apps," "cut your tool stack in half," "one place")</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Zero-risk entry offers as the standard CTA (free forever, start free, 30-day free trial)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Anti-spreadsheet / anti-manual-work framing as the implied status quo enemy</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Star ratings with review counts (Nike, Alo, Under Armour, Tracksmith, Arc'teryx) — though volumes range wildly from 22 to 21,131 reviews</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Percentage-off and dollar-entry offers (Fabletics, Under Armour, New Balance, Patagonia)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Shipping and returns reassurance — free shipping, free returns, 30-day windows (On, Gymshark, Arc'teryx, Vuori, Tracksmith)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Named proprietary technology (UA HOVR, On LightSpray, New Balance Infinion Foam)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Fabric-performance descriptors used as de facto proof: sweat-wicking, breathable, anti-stink, lightweight</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Heritage and durability guarantees (New Balance 'Established 1906', Patagonia 'Made to Last', Tracksmith 'Designed in Boston')</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>RECOMMENDATIONS</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="48" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Own the enterprise trust lane with a security-and-governance campaign targeted at IT and security buyers, gated on a compliance pack rather than a free trial.
-Why: It is the single largest gap in the matrix and it points at the segment with the highest ACV and lowest churn. Competing head-on for SMB free signups means fighting ClickUp's price message and Monday's brand spend with no differentiation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="48" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Stop competing on 'performance + comfort' copy and rebuild the top-line claim around belonging plus proven durability. Launch a named, dated community program for one specific under-served tribe (size-inclusive strength training, studio, or the everyday non-elite runner) and put its metrics — members, cities, sessions — into the ads as the proof point.
+Why: Performance is claimed by 11 of 12 brands and comfort by 9, with almost identical wording; that parity is what forces the discounting already visible at Fabletics and Under Armour. Community appears in just three ads across the whole set and only Gymshark treats it seriously, which leaves every audience outside the weight room unowned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Make human support a headline claim with a specific, falsifiable commitment — a response-time SLA, a named onboarding lead, or a migration-done-for-you offer.
-Why: Every competitor sells consolidation but none address the cost and risk of actually consolidating. Support is unclaimed, cheap to prove, and directly de-risks the biggest objection to switching platforms.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="48" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Fix the proof gap immediately: publish a review count with rating on every ad, and add one concrete, verifiable durability or delivery promise (e.g. a multi-year wear guarantee or a stated delivery window) to the core creative.
+Why: Vuori and lululemon cite no proof at all, and several rivals lean on tiny samples (Arc'teryx 24 reviews, Tracksmith 22). Nike's 6,660-review rating plus 1-3 day delivery and Alo's 21,131 reviews show the bar that actually converts. A hard guarantee also gives sustainability a credible spine — Patagonia is the only brand making 'made to last' do commercial work, and it is doing it in a single ad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Replace generic customer-count claims with outcome proof tied to a named segment — a specific customer, a specific number, a specific timeframe.
-Why: "X teams trust us" is now category wallpaper and a volume contest ClickUp wins at 2 million. Only ClickUp uses an outcome stat, and it's vague. Concrete, attributed results cut through a field of interchangeable trust badges.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="48" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>4.</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Cede the "all-in-one" framing and reposition against consolidation fatigue — depth and reliability in the workflows that actually matter, rather than replacing ten apps.
-Why: Integrations/all-in-one is the most crowded theme in the matrix (7 ads across 3 brands). Buyers who have already tried and abandoned an everything-app are an addressable, resentful audience no one is speaking to.</t>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Target the two thinnest audience pockets — yoga/studio (only two ads in the entire set) and size-inclusive (only Fabletics, and only as a price play) — with dedicated product and creative rather than folding them into a general women's line.
+Why: Everyday athleisure is saturated (Vuori 4, lululemon 4, New Balance 3, Alo 2, Gymshark 2) and outdoor is locked up by Arc'teryx and Patagonia. Studio and size-inclusive are large, high-repeat segments where the only incumbent voice is a discount brand, so a premium, proof-backed entrant can win share without buying it on promotion.</t>
         </is>
       </c>
     </row>
@@ -733,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -755,155 +861,386 @@
       </c>
       <c r="B1" s="6" t="inlineStr">
         <is>
+          <t>Performance / Technical fabric</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Comfort / Feel</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Style / Design</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>Sustainability</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
           <t>Price / Value</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
-        <is>
-          <t>Speed / Efficiency</t>
-        </is>
-      </c>
-      <c r="D1" s="6" t="inlineStr">
-        <is>
-          <t>Ease of Use</t>
-        </is>
-      </c>
-      <c r="E1" s="6" t="inlineStr">
-        <is>
-          <t>Integrations / All-in-one</t>
-        </is>
-      </c>
-      <c r="F1" s="6" t="inlineStr">
-        <is>
-          <t>Trust / Scale</t>
-        </is>
-      </c>
-      <c r="G1" s="7" t="inlineStr">
-        <is>
-          <t>Customer Support</t>
-        </is>
-      </c>
-      <c r="H1" s="7" t="inlineStr">
-        <is>
-          <t>Enterprise / Security</t>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>Innovation / New technology</t>
         </is>
       </c>
       <c r="I1" s="6" t="inlineStr">
         <is>
-          <t>Innovation / AI</t>
+          <t>Community / Belonging</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>Asana</t>
-        </is>
-      </c>
-      <c r="B2" s="9" t="n"/>
-      <c r="C2" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="10" t="n">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Alo Yoga</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="8" t="n"/>
+      <c r="H2" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="8" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Arc'teryx</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E2" s="10" t="n">
+      <c r="C3" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="8" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Fabletics</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="F2" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="11" t="n"/>
-      <c r="H2" s="11" t="n"/>
-      <c r="I2" s="10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>ClickUp</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="n">
+      <c r="C4" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="9" t="n"/>
-      <c r="E3" s="10" t="n">
+      <c r="E4" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Gymshark</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F3" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="9" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Monday.com</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="n"/>
-      <c r="C4" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="10" t="n">
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="8" t="n"/>
+      <c r="H5" s="8" t="n"/>
+      <c r="I5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="10" t="n">
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>New Balance</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="F4" s="9" t="n"/>
-      <c r="G4" s="11" t="n"/>
-      <c r="H4" s="11" t="n"/>
-      <c r="I4" s="9" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="C6" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+      <c r="H6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="8" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Patagonia</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="8" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Tracksmith</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Under Armour</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="8" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Vuori</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>lululemon</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B5" s="12">
-        <f>SUM(B2:B4)</f>
+      <c r="B14" s="10">
+        <f>SUM(B2:B13)</f>
         <v/>
       </c>
-      <c r="C5" s="12">
-        <f>SUM(C2:C4)</f>
+      <c r="C14" s="10">
+        <f>SUM(C2:C13)</f>
         <v/>
       </c>
-      <c r="D5" s="12">
-        <f>SUM(D2:D4)</f>
+      <c r="D14" s="10">
+        <f>SUM(D2:D13)</f>
         <v/>
       </c>
-      <c r="E5" s="12">
-        <f>SUM(E2:E4)</f>
+      <c r="E14" s="10">
+        <f>SUM(E2:E13)</f>
         <v/>
       </c>
-      <c r="F5" s="12">
-        <f>SUM(F2:F4)</f>
+      <c r="F14" s="10">
+        <f>SUM(F2:F13)</f>
         <v/>
       </c>
-      <c r="G5" s="13">
-        <f>SUM(G2:G4)</f>
+      <c r="G14" s="10">
+        <f>SUM(G2:G13)</f>
         <v/>
       </c>
-      <c r="H5" s="13">
-        <f>SUM(H2:H4)</f>
+      <c r="H14" s="10">
+        <f>SUM(H2:H13)</f>
         <v/>
       </c>
-      <c r="I5" s="12">
-        <f>SUM(I2:I4)</f>
+      <c r="I14" s="10">
+        <f>SUM(I2:I13)</f>
         <v/>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>Cell = number of that brand's ads using the theme. Blue = a theme in play. Peach columns = whitespace (no competitor is using it).</t>
         </is>
@@ -920,7 +1257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -942,141 +1279,358 @@
       </c>
       <c r="B1" s="6" t="inlineStr">
         <is>
-          <t>Small business</t>
-        </is>
-      </c>
-      <c r="C1" s="7" t="inlineStr">
-        <is>
-          <t>Enterprise / IT</t>
-        </is>
-      </c>
-      <c r="D1" s="7" t="inlineStr">
-        <is>
-          <t>Marketing teams</t>
-        </is>
-      </c>
-      <c r="E1" s="7" t="inlineStr">
-        <is>
-          <t>Sales teams</t>
-        </is>
-      </c>
-      <c r="F1" s="7" t="inlineStr">
-        <is>
-          <t>Developers / Technical</t>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Men</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Runners</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Yoga &amp; studio</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>Gym &amp; strength training</t>
         </is>
       </c>
       <c r="G1" s="6" t="inlineStr">
         <is>
-          <t>Operations / Project managers</t>
-        </is>
-      </c>
-      <c r="H1" s="7" t="inlineStr">
-        <is>
-          <t>Executives / Leadership</t>
+          <t>Outdoor &amp; hiking</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>Everyday / athleisure</t>
         </is>
       </c>
       <c r="I1" s="6" t="inlineStr">
         <is>
-          <t>General / Everyone</t>
+          <t>Size-inclusive</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>Asana</t>
-        </is>
-      </c>
-      <c r="B2" s="9" t="n"/>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="11" t="n"/>
-      <c r="G2" s="10" t="n">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Alo Yoga</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="8" t="n"/>
+      <c r="H2" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" s="8" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Arc'teryx</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" s="8" t="n"/>
+      <c r="I3" s="8" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Fabletics</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="8" t="n"/>
+      <c r="F4" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Gymshark</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="8" t="n"/>
+      <c r="H5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" s="8" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>New Balance</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+      <c r="H6" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="H2" s="11" t="n"/>
-      <c r="I2" s="9" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>ClickUp</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="n">
+      <c r="I6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="n"/>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="11" t="n"/>
-      <c r="G3" s="9" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Monday.com</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="n">
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="11" t="n"/>
-      <c r="G4" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="11" t="n"/>
-      <c r="I4" s="9" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+      <c r="H7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="8" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Patagonia</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" s="8" t="n"/>
+      <c r="I9" s="8" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Tracksmith</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Under Armour</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+      <c r="H11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="8" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Vuori</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>lululemon</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B5" s="12">
-        <f>SUM(B2:B4)</f>
+      <c r="B14" s="10">
+        <f>SUM(B2:B13)</f>
         <v/>
       </c>
-      <c r="C5" s="13">
-        <f>SUM(C2:C4)</f>
+      <c r="C14" s="10">
+        <f>SUM(C2:C13)</f>
         <v/>
       </c>
-      <c r="D5" s="13">
-        <f>SUM(D2:D4)</f>
+      <c r="D14" s="10">
+        <f>SUM(D2:D13)</f>
         <v/>
       </c>
-      <c r="E5" s="13">
-        <f>SUM(E2:E4)</f>
+      <c r="E14" s="10">
+        <f>SUM(E2:E13)</f>
         <v/>
       </c>
-      <c r="F5" s="13">
-        <f>SUM(F2:F4)</f>
+      <c r="F14" s="10">
+        <f>SUM(F2:F13)</f>
         <v/>
       </c>
-      <c r="G5" s="12">
-        <f>SUM(G2:G4)</f>
+      <c r="G14" s="10">
+        <f>SUM(G2:G13)</f>
         <v/>
       </c>
-      <c r="H5" s="13">
-        <f>SUM(H2:H4)</f>
+      <c r="H14" s="10">
+        <f>SUM(H2:H13)</f>
         <v/>
       </c>
-      <c r="I5" s="12">
-        <f>SUM(I2:I4)</f>
+      <c r="I14" s="10">
+        <f>SUM(I2:I13)</f>
         <v/>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>Cell = number of that brand's ads aimed at the audience. Peach columns = audiences no competitor is speaking to.</t>
         </is>
@@ -1093,7 +1647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1119,59 +1673,370 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>Asana</t>
-        </is>
-      </c>
-      <c r="B2" s="15" t="inlineStr">
-        <is>
-          <t>85% of the Fortune 100 trust Asana</t>
-        </is>
-      </c>
-      <c r="C2" s="9" t="n">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Alo Yoga</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>3.1 rating from 35 reviews</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>ClickUp</t>
-        </is>
-      </c>
-      <c r="B3" s="15" t="inlineStr">
-        <is>
-          <t>Save a day every week</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="n">
+      <c r="A3" s="12" t="inlineStr"/>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>30+ days returnable</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr"/>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>Trusted by 2 million teams</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="n">
+      <c r="A4" s="12" t="inlineStr"/>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>4.5 rating from 21,131 reviews</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>Monday.com</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>225,000+ teams trust monday.com</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="n">
-        <v>1</v>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Arc'teryx</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Rating 4.0 from 24 reviews</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Fabletics</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>$15 for new Fabletics VIPs</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr"/>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>50% off Jackets and Vests</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr"/>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>50% off Underscrubs</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>80% Off everything</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr"/>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Swimsuits for $19 as a New VIP</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Gymshark</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Free Returns</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>New Balance</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>25% Off Select Shoes</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr"/>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Established in 1906</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr"/>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Extended Widths</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr"/>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>New Infinion Foam Midsole</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr"/>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Up to 30% Off Select Clothing and Accessories</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Average delivery time 1-3 days</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr"/>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Rating 4.7 from 6,660 reviews</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>30-day Returns</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr"/>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>Free Shipping</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr"/>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>Maximum cushioning</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Patagonia</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Guaranteed Quality</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr"/>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Made to Last</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr"/>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>Up to 40% Off</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Tracksmith</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>Rating 5.0 from 22 reviews</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Under Armour</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>25% off UA back-to-school deals valid Jul 19 to Aug 21</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr"/>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>30-50% Off Sitewide</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr"/>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>4.7 rating from 305 reviews</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Vuori</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>(no concrete proof points cited)</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>lululemon</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>(no concrete proof points cited)</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1185,7 +2050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1235,315 +2100,1440 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
-        <is>
-          <t>Asana</t>
-        </is>
-      </c>
-      <c r="B2" s="15" t="inlineStr">
-        <is>
-          <t>Manage your team's work in one place. Asana keeps projects on track with timelines, automation, and clear ownership. Start free.</t>
-        </is>
-      </c>
-      <c r="C2" s="15" t="inlineStr">
-        <is>
-          <t>Ease of Use, Integrations / All-in-one</t>
-        </is>
-      </c>
-      <c r="D2" s="15" t="inlineStr">
-        <is>
-          <t>Operations / Project managers</t>
-        </is>
-      </c>
-      <c r="E2" s="15" t="inlineStr"/>
-      <c r="F2" s="15" t="inlineStr">
-        <is>
-          <t>Search</t>
-        </is>
-      </c>
-      <c r="G2" s="15" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>lululemon</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>lululemon Women's Tank Tops - lululemon Tank Tops For Women. Our Tank-Tops Were Made To Run In, Train In, Flow In, And Relax In. Some That Do It All. Sweat-Wicking, Breathable, Anti-Stink.</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Versatility / Gym-to-street, Comfort / Feel</t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
+        <is>
+          <t>Women, Runners, Yoga &amp; studio, Gym &amp; strength training, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="inlineStr"/>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>Asana</t>
-        </is>
-      </c>
-      <c r="B3" s="15" t="inlineStr">
-        <is>
-          <t>Less busywork, more impact. Automate routine tasks and hit every deadline. Trusted by 85% of the Fortune 100.</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>Speed / Efficiency, Ease of Use, Trust / Scale, Innovation / AI</t>
-        </is>
-      </c>
-      <c r="D3" s="15" t="inlineStr">
-        <is>
-          <t>Operations / Project managers</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>85% of the Fortune 100 trust Asana</t>
-        </is>
-      </c>
-      <c r="F3" s="15" t="inlineStr">
-        <is>
-          <t>Search</t>
-        </is>
-      </c>
-      <c r="G3" s="15" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>lululemon</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>lululemon Official Site - lululemon Women's Clothing. You're This Close To Versatile Shorts That Look As Good As They Feel. In Shorts This Lightweight.</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>Comfort / Feel</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>Women, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr"/>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>Asana</t>
-        </is>
-      </c>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>See who is doing what by when. Every project gets a clear owner and due date. Try Asana free for 30 days.</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="inlineStr">
-        <is>
-          <t>Ease of Use, Integrations / All-in-one</t>
-        </is>
-      </c>
-      <c r="D4" s="15" t="inlineStr">
-        <is>
-          <t>Operations / Project managers</t>
-        </is>
-      </c>
-      <c r="E4" s="15" t="inlineStr"/>
-      <c r="F4" s="15" t="inlineStr">
-        <is>
-          <t>Display</t>
-        </is>
-      </c>
-      <c r="G4" s="15" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>lululemon</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Leggings Fit For Every Move - lululemon Official Site. Make Better Leggings Your Base. Then Style And Move The Way You Want In Total Comfort.</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Comfort / Feel, Style / Design, Versatility / Gym-to-street, Innovation / New technology</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>Women, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr"/>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>Monday.com</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>The Work OS that adapts to you. Build any workflow, no code required. Get started free.</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="inlineStr">
-        <is>
-          <t>Ease of Use, Integrations / All-in-one</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
-        <is>
-          <t>Small business</t>
-        </is>
-      </c>
-      <c r="E5" s="15" t="inlineStr"/>
-      <c r="F5" s="15" t="inlineStr">
-        <is>
-          <t>Search</t>
-        </is>
-      </c>
-      <c r="G5" s="15" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>lululemon</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>lululemon Official Site. Stores Globally. We Made Too Much. Like New Resale Program.</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Price / Value, Sustainability</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr"/>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>Monday.com</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>Ditch the spreadsheets. Manage projects, sales, and marketing on one colorful platform. 225,000+ teams trust monday.com.</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>Ease of Use, Integrations / All-in-one</t>
-        </is>
-      </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>Small business</t>
-        </is>
-      </c>
-      <c r="E6" s="15" t="inlineStr">
-        <is>
-          <t>225,000+ teams trust monday.com</t>
-        </is>
-      </c>
-      <c r="F6" s="15" t="inlineStr">
-        <is>
-          <t>Display</t>
-        </is>
-      </c>
-      <c r="G6" s="15" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Womens Dri-FIT Running Shorts. Nike.com. Shop The Official Nike Store For The Latest Nike Shoes, Apparel and Gear. Live Support Available. Styles: Shoes, Clothing, Accessories, Sport. Rating 4.7 from 6,660 reviews. Average delivery time 1-3 days.</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Comfort / Feel, Style / Design, Price / Value, Innovation / New technology</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Women, Runners</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Rating 4.7 from 6,660 reviews, Average delivery time 1-3 days</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>Monday.com</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>Automate the busywork. Set it once and let monday.com handle the follow-ups. Start your free trial.</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>Speed / Efficiency</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>Operations / Project managers</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="inlineStr"/>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>Search</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Womens Golf Shoes. Nike.com. Shop Womens Golf Shoes Designed With Comfort, Style and Performance In Mind. Gear Up For Sport And Style With Nike Products Designed For Performance And Comfort. Live Support Available.</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Comfort / Feel, Style / Design</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr"/>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>ClickUp</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>One app to replace them all. Docs, tasks, goals, and chat in one place. Save a day every week. Free forever.</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>Integrations / All-in-one, Speed / Efficiency, Price / Value</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>Small business</t>
-        </is>
-      </c>
-      <c r="E8" s="15" t="inlineStr">
-        <is>
-          <t>Save a day every week</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="inlineStr">
-        <is>
-          <t>Search</t>
-        </is>
-      </c>
-      <c r="G8" s="15" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Golf Gloves and Mitts. Nike.com. Shop The Official Nike Store For The Latest Nike Shoes, Apparel and Gear. Gear Up For Sport And Style With Nike Products Designed For Performance And Comfort.</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Comfort / Feel</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr"/>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>ClickUp</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>The everything app for work. Bring your team's tools together. Trusted by 2 million teams.</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>Integrations / All-in-one, Trust / Scale</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>General / Everyone</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="inlineStr">
-        <is>
-          <t>Trusted by 2 million teams</t>
-        </is>
-      </c>
-      <c r="F9" s="15" t="inlineStr">
-        <is>
-          <t>Display</t>
-        </is>
-      </c>
-      <c r="G9" s="15" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Soccer Jerseys. Nike.com. Gear Up For Soccer. Get Everything You Need For Your Best Season Ever. Shop The Latest Soccer Gear For A Fresh Start On The Field. Start Back Strong. Live Support Available. Models: Air Force 1, VaporMax, Air Max, Pegasus, Joyride, Vaporfly, React.</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Runners</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr"/>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>ClickUp</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>Cut your tool stack in half. ClickUp does the work of ten apps. Get started free.</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>Integrations / All-in-one, Price / Value</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="inlineStr">
-        <is>
-          <t>Small business</t>
-        </is>
-      </c>
-      <c r="E10" s="15" t="inlineStr"/>
-      <c r="F10" s="15" t="inlineStr">
-        <is>
-          <t>Search</t>
-        </is>
-      </c>
-      <c r="G10" s="15" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Alo Yoga</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Denim Knit Mini Dress - Black/Anthracite. Crafted from soft, structured, ribbed-knit fabric inspired by the nuanced texture of denim, this mini dress takes your going-out looks to great lengths. Rating 4.5 from 21,131 reviews. Most items returnable 30+ days.</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Comfort / Feel, Style / Design, Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Women, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>4.5 rating from 21,131 reviews, 30+ days returnable</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Alo Yoga</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>ALO Official Site - Performance Ready Activewear. Go from studio to street. ALO men's shorts deliver buttery-soft comfort and an active fit. Celeb-approved training shorts, trending for dynamic, empowered movement.</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Comfort / Feel, Style / Design, Versatility / Gym-to-street, Innovation / New technology</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>Men, Yoga &amp; studio, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr"/>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Alo Yoga</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>ALO. Clothing store. Open now. Call or get Directions. Rating 3.1 from 35 reviews.</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr"/>
+      <c r="D12" s="12" t="inlineStr"/>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>3.1 rating from 35 reviews</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Vuori</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Shop Vuori Performance Gear - Vuori Clothing. A New Perspective on Performance Apparel. An Integration Of Fitness, Surf and Sport. Premium Performance Apparel, Without Sacrificing Comfort.</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Comfort / Feel, Style / Design, Versatility / Gym-to-street, Innovation / New technology</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>Men, Women, Gym &amp; strength training, Outdoor &amp; hiking, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr"/>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Vuori</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Women's Sweatpants - Your New Favorite Sweatpants. Achieve Maximum Comfort With Vuori Sweatpants. You'll Never Want To Take Them Off. Designed For Style, Comfort and Performance. Free Shipping.</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Comfort / Feel, Style / Design, Performance / Technical fabric, Price / Value</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>Women, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr"/>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Vuori</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Vuori Clothing - Official Site. A New Perspective On Performance Apparel. Free Shipping On Orders $75+. Shop Men's And Women's Performance Apparel. Built To Move In. Styled For Life.</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Style / Design, Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>Women, Men, Gym &amp; strength training, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr"/>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Vuori</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Vuori Clothing - Comfort For Your Active Life. A New Perspective On Performance Apparel. Free Shipping On Orders $75+. Shop Men's And Women's Performance Apparel. Built To Move In. Styled For Life.</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Comfort / Feel, Style / Design, Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Women, Men, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr"/>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>On Official Store - Free Shipping. 30-day Returns. Runners that want to double up on cushioning and support without slowing down. Maximum cushioning.</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Comfort / Feel</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>Runners</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>Free Shipping, 30-day Returns, Maximum cushioning</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>On's Waterproof Collection - Discover Our Waterproof Shoes. Element-proof Swiss-engineering. Shelter from the storm. Get rain ready. Seasons change. Trainings shouldn't. Master the elements with our waterproof gear. Wet weather gear: high-tech jackets, shoes and accessories to beat the elements. All-day sneakers: unbeatable comfort for the city, travel or everyday exploring.</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Comfort / Feel, Versatility / Gym-to-street, Innovation / New technology</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Runners, Outdoor &amp; hiking, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr"/>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>Cloudboom Strike 2 LS - Run On Clouds - On Official Store. The pinnacle marathon racing shoe for fast-feeling comfort. Updated LightSpray upper for a seamless, adaptive fit. Limited editions.</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Comfort / Feel, Innovation / New technology</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>Runners</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr"/>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>On Official Store - Free Shipping. Updated shape, structure and volume for superior comfort, cushioning and stability.</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Comfort / Feel, Performance / Technical fabric, Innovation / New technology</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Gym &amp; strength training</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr"/>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Under Armour</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>Zero Gravity Feel - 30-50% Off Sitewide. Energy Return That Helps Eliminate Impact Step After Step. Shop The UA HOVR Collection, The Perfect Balance Between Sport and Style. Rating 4.7 from 305 reviews. UA HOVR Cushioning: connected technology and revolutionary cushioning designed by those who know. UA HOVR Infinite 2: more coaching, more miles, go further and faster. Too Comfy To Be Slowed Down.</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Comfort / Feel</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>Runners</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>30-50% Off Sitewide, 4.7 rating from 305 reviews</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Under Armour</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>The Official Site - Join UA Rewards. Get The Gear Everyone's After. Shop Under Armour Training Gear Today. Experience Superior Comfort and Durability. Women's Apparel. Men's Apparel. 25% Off BTS Gear. 25% off UA back-to-school deals valid Jul 19 to Aug 21.</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Comfort / Feel, Price / Value</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Women, Men, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>25% off UA back-to-school deals valid Jul 19 to Aug 21</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Gymshark</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Gymshark Official Store - Gym Clothes Store. Unlock your full potential with our game-changing workout clothes. Shop gym clothing for the gym, running and everything in-between. New Releases. Free Returns.</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Women, Men, Gym &amp; strength training, Runners, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>Free Returns</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Gymshark</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>Socks Are We Supposed To Be Wearing? The Great Gen Z Debate. Are ankle socks out of style? TikTok might be telling you they are a millennial giveaway, read on to find out whether it's time to swap them out for Crew socks. New Releases.</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Style / Design, Community / Belonging, Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>Women, Men, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr"/>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Gymshark</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>Gymshark - We Do Gym - The Gym Is Everything We Do. Your New PBs Will Look Good In A Fresh New Gymshark Fit. Get Yours Now. However You Gym, We've Got The Clothes, Accessories and Community.</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Style / Design, Versatility / Gym-to-street, Community / Belonging</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>Gym &amp; strength training</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr"/>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Arc'teryx</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>Arc'teryx Outerwear - Products made for performance - Outlast the sun. Protect your skin with Arc'teryx men's sun protective clothing collection. Stay shielded from the sun and cool from the heat with breathable, protective gear. High-Performance Apparel. Free Shipping and Returns. Men's Collection. Women's Collection. Arc'teryx New Arrivals.</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Comfort / Feel</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>Men, Women, Outdoor &amp; hiking</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr"/>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Arc'teryx</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>It's the season of long days. Made with lightweight fabrics and built-in sun protection for long days. Outdoor clothing and equipment shop, Aspen, 534 East Cooper Avenue.</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>Outdoor &amp; hiking</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr"/>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Arc'teryx</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>Lightweight gear - Made for trails. Lightweight by design, these technical shells are built for fast vertical gain. Grab the season's best breathable layers and fast-drying fabrics to chase daylight.</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Innovation / New technology</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>Outdoor &amp; hiking</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr"/>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Arc'teryx</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>Arc'teryx Fashion Island. Outdoor clothing and equipment shop, Newport Beach. Rating 4.0 from 24 reviews. Shop preloved clothing and gear from your favorite brand to save your wallet and landfill.</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>Sustainability, Price / Value</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>Outdoor &amp; hiking</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>Rating 4.0 from 24 reviews</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Patagonia</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>Patagonia Gear Made to Last - Built for Years, Not Seasons. Guaranteed Quality and Profits Go to the Planet. Shop Patagonia Clothing and Gear. Explore Quality Patagonia Clothing and Gear for Snow, Surfing.</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Sustainability, Innovation / New technology</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>Outdoor &amp; hiking</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>Guaranteed Quality, Made to Last</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>Patagonia</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>Travel Duffel Bags - Patagonia Duffel Bags. Travel Duffel Bags That Swallow All the Gear in Your Van with Room for Half Your Garage. Be It a Fun-Hog outing or an expedition.</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>Outdoor &amp; hiking</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr"/>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>Patagonia</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>Up to 40% Off. Need a Break? Select Styles Are Now On Sale. Now's the Time to Get Your Fill. Outdoor clothing and equipment shop, Encinitas, 2185 San Elijo Avenue.</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>Price / Value</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>Outdoor &amp; hiking</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>Up to 40% Off</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Tracksmith</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>Stay Ready For Race Day - Essentials For Serious Runners. Running Bottoms Designed In Boston To Meet The Rigorous Demands Of Runners Everywhere. Discover Tracksmith Running Bottoms. Crafted For The Pursuit Of Personal Excellence. Rating 5.0 from 22 reviews. Spring 26 Collection.</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Style / Design</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>Runners</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>Rating 5.0 from 22 reviews</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Tracksmith</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>Tracksmith Running Tights - Running Tops, Shorts and More. Tracksmith Running Gear Is Designed In Boston To Meet The Demands Of Runners Everywhere. Shop Tracksmith For Running Tops, Bottoms And More. View 5 prices from $54.00.</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Style / Design, Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>Runners</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr"/>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Tracksmith</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>Next-Level Running Apparel - High Performance Running Pants. Running Essentials To Keep You Race Day Ready. Free Shipping On Orders Over $150. Built to Last and Made for Miles, These are the Staples We Run All Year.</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>Runners</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr"/>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Tracksmith</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>Tracksmith - Made For Mileage - Running Tops, Shorts and More. Discover Tracksmith, Running Apparel Crafted For The Pursuit Of Personal Excellence. Shop Men's Running Best Sellers. Women's Collection. Running Footwear. 20% Off Your First Order. Remarkable Running Shoes.</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Style / Design</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>Women, Men, Runners</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr"/>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>New Balance</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>New Balance Lifestyle - Shop The Lifestyle Collection. New Balance Lifestyle Is Your Go-To Place For Daily Footwear. Shop The Collection Now. Up to 30% Off Select Clothing and Accessories and 25% Off Select Shoes. New Balance 992 Exemplifies Craftsmanship Inside And Out.</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>Style / Design, Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>Up to 30% Off Select Clothing and Accessories, 25% Off Select Shoes</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>New Balance</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>New Balance Back to School - Back to School Shopping. From Backpacks To Apparel New Balance Has All The Styles For The School Year Ahead. Time To Upgrade and Update With New Balance Back To School Styles.</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>Style / Design, Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr"/>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>New Balance</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>New Balance 1080v15 - New Balance Running Collection. A Whole New Way Of Looking At The Most Comfortable Running Shoe We Can Make, Period. A New Way To Experience Everything You Rely On In An Everyday Running Shoe. Extended Widths. New Infinion Foam Midsole. Contoured Details. Established In 1906.</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Comfort / Feel, Versatility / Gym-to-street, Innovation / New technology</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>Runners, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>Established in 1906, New Infinion Foam Midsole, Extended Widths</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>New Balance</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>4040 Baseball Cleat - Men's Cleats. The 4040 Baseball Shoe That Delivers Traction To Bring Ultimate Performance. Combined The Function And Comfort Sought By Every Level Of Baseball Player.</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Comfort / Feel</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>Men</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr"/>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>Fabletics</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>Stop Overpaying for Activewear - Online Activewear For Men. Sweat in Style: Fabletics Men's Activewear for Every Workout. Versatile Performance Pieces Armed with All the Essentials to Train, Travel or Trailblaze. Anti-Stink.</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Style / Design, Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>Men, Gym &amp; strength training, Outdoor &amp; hiking, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr"/>
+      <c r="F41" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>Fabletics</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>Affordable Green Scrubs - First Scrub Set for $15. Our scrub sets are breathable, lightweight and wrinkle resistant. $15 for new Fabletics VIPs. 50% off Underscrubs. 50% off Jackets and Vests. Exclusive $15 Set for New VIPs. Built-In Bra Scrub Top.</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>Price / Value, Performance / Technical fabric, Sustainability</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>Women, Size-inclusive</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="inlineStr">
+        <is>
+          <t>$15 for new Fabletics VIPs, 50% off Underscrubs, 50% off Jackets and Vests</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>Fabletics</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>Swimsuits for $19 as a New VIP - Swim Tops for Big Busts. Active swim styles designed for support, stretch, and confidence. Get 80% Off everything when you sign up as a VIP.</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>Price / Value, Comfort / Feel, Style / Design, Community / Belonging</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>Women, Size-inclusive</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>Swimsuits for $19 as a New VIP, 80% Off everything</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>

--- a/output/messaging_matrix.xlsx
+++ b/output/messaging_matrix.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -519,7 +519,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Every brand in this set is selling some blend of performance, comfort and versatility, and almost none are backing it with hard evidence — the category's discipline gap is proof, not positioning, with community and sustainability the least-defended themes.</t>
+          <t>Every brand in the category is selling comfort, versatility and technical performance in nearly identical language — the only genuinely under-claimed territories are community/belonging (5 ads across 3 brands) and durability/sustainability, which means differentiation now comes from proof, not adjectives.</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Community / Belonging is the least crowded theme in the set — only Gymshark and Tracksmith touch it, one ad each — and it is the one claim a competitor cannot copy by reformulating a fabric. The adjacent gap is verified performance proof: 11 of 12 brands claim technical performance, but the only substantiation in market is star ratings, free shipping and discounts. Nobody is proving a performance claim with a number, a test, or a named athlete outcome.</t>
+          <t>Community and identity are the least crowded themes: only Gymshark (3), Alo (1) and Tracksmith (1) make any belonging claim, and only Gymshark ties it to a real subculture. Sustainability is similarly thin (lululemon 4, On 2, everyone else 0–1) and is currently claimed as a compliance footnote rather than a reason to buy. Meanwhile 'comfort' and 'gym-to-street versatility' carry roughly 70 of the ads in this set with interchangeable copy — 'buttery-soft,' 'built to move in, styled for life,' 'looks as good as it feels.'</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Fabric and comfort claims have collapsed into undifferentiated wallpaper — 'buttery-soft', 'sweat-wicking', 'built to move in' appear in near-identical form across Alo, Vuori, lululemon and Fabletics, so paid clicks are being won on price and shipping terms instead of brand. That drags the whole category toward promo dependency, which is exactly where Fabletics and Under Armour already live (80% off, 30-50% off sitewide). A brand that owns belonging plus verifiable proof escapes the discount treadmill and defends full price.</t>
+          <t>Undifferentiated comfort/versatility claims force competition on discount depth, which is exactly where Under Armour (50% off, 30–50% off sitewide), Fabletics ($15 sets, 80% off) and New Balance (30% off) already live. Ads anchored in identity and provenance defend full price: Tracksmith holds a $54 floor on 'Designed in Boston,' and Patagonia sells on 'Built for Years, Not Seasons' with almost no feature copy at all. Belonging also compounds — it drives repeat purchase and organic content rather than one-time conversion.</t>
         </is>
       </c>
     </row>
@@ -562,7 +562,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Build a campaign line around a named, specific community with measurable proof attached — e.g. a run club, training program or member challenge with published participation numbers, completion rates and member-submitted results — and put those numbers directly in the ad copy where competitors put discount percentages. Pair it with one hard performance metric per hero product (grams, energy return, wash-cycle durability, tested wicking rate) so the community claim is evidenced, not sentimental.</t>
+          <t>Build a campaign line around who the customer is and what they belong to, not how the fabric feels — a named crew, level, or place (city runs, lifting groups, a training program) with member proof in the ad unit: participation numbers, meetup cadence, user-submitted results. Pair it with a durability guarantee claim ('built for X years' or a lifetime repair promise) so the identity story has a hard commercial fact attached and the ad stops competing on softness.</t>
         </is>
       </c>
     </row>
@@ -576,168 +576,168 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>lululemon</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>The default everything store: performance and comfort across every sport, with scale and service as the reassurance.
-Targets: Women, runners and everyday wearers — broad rather than niche.
-Signature proof: 4.7 rating from 6,660 reviews plus 1-3 day average delivery.</t>
+          <t>The default all-day wardrobe — one garment that runs, trains, flows and relaxes, with the broadest claim set in the category.
+Targets: Women and everyday athleisure buyers above all (12 women, 13 everyday ads)
+Signature proof: Functional triad: sweat-wicking, breathable, anti-stink</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>lululemon</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>One garment for every part of the day — versatility is their dominant and near-exclusive claim.
-Targets: Women first, with secondary reach into men, yoga/studio, gym and everyday.
-Signature proof: Functional fabric triad: sweat-wicking, breathable, anti-stink.</t>
+          <t>Generic sport-and-style authority; ads lean on store credibility rather than a distinct product argument.
+Targets: Split evenly across women, men, runners and gym; no clear focus
+Signature proof: 4.7 rating from 6,660 reviews and 1–3 day delivery</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Vuori</t>
+          <t>Alo Yoga</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Performance apparel restyled for life — the widest claim and audience spread of any brand here.
-Targets: Broadest in the set: women, men, runners, yoga, gym, outdoor, everyday.
-Signature proof: None cited — only free shipping over $75; the biggest proof gap in the group.</t>
+          <t>Studio-to-street fashion activewear with celebrity social proof standing in for performance evidence.
+Targets: Women, yoga/studio and everyday athleisure
+Signature proof: 4.5 rating from 21,615 reviews plus 'Celeb-approved'</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>On</t>
+          <t>Vuori</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Swiss-engineered running innovation, extending into all-day and weather-proof wear.
-Targets: Runners primarily, plus everyday, gym and outdoor.
-Signature proof: Product-level engineering specifics (LightSpray upper, maximum cushioning) backed by free shipping and 30-day returns.</t>
+          <t>Premium performance apparel that refuses to sacrifice comfort — the most style-forward technical claim in the set.
+Targets: Balanced men and women, heavily everyday/athleisure
+Signature proof: 120+ day returns and 4.6 from 14,413 reviews</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Arc'teryx</t>
+          <t>On</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Uncompromising technical outerwear for the mountains, sold on fabric science.
-Targets: Outdoor and hiking, split evenly across men and women.
-Signature proof: Thin: 4.0 rating from 24 reviews — the technical story carries the weight.</t>
+          <t>Swiss-engineered innovation — the only brand where new technology is a lead message, not a footnote (8 innovation ads).
+Targets: Runners, outdoor and everyday sneaker buyers
+Signature proof: Named engineering detail: LightSpray upper, new sockliner, Swiss-engineered</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Tracksmith</t>
+          <t>Under Armour</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Craft running apparel for serious runners, anchored in Boston heritage.
-Targets: Runners, narrowly and deliberately.
-Signature proof: 5.0 rating from 22 reviews, 'Designed in Boston', prices from $54.</t>
+          <t>Performance tech sold through discount urgency; the promotion is the headline.
+Targets: Gym and strength training, men skewed
+Signature proof: '50% Off, 2X A Year' semi-annual event</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Under Armour</t>
+          <t>Gymshark</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Cushioning and energy-return technology sold at a permanent discount.
-Targets: Gym and strength trainers, plus runners, men and women.
-Signature proof: 30-50% off sitewide and 4.7 from 305 reviews — price does the persuading.</t>
+          <t>Gym culture as identity — 'We Do Gym' plus community and content, not just clothing.
+Targets: Gym and strength training, everyday wear, plus a growing runner push
+Signature proof: Community-led editorial content and Pay in 4 / student discount access</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Fabletics</t>
+          <t>Arc'teryx</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>The value play: don't overpay for activewear, with membership pricing as the hook.
-Targets: Women first, plus men, gym, outdoor and explicitly size-inclusive.
-Signature proof: $15 first scrub set, $19 swimsuits, 80% off for new VIPs.</t>
+          <t>Uncompromising technical outerwear for real mountain conditions — the purest performance play (11 of 20 ads).
+Targets: Outdoor and hiking almost exclusively (12 ads)
+Signature proof: GORE-TEX ePE membrane and The Arc'teryx Guarantee</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Gymshark</t>
+          <t>Patagonia</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>The gym is the identity — culture and community over fabric claims.
-Targets: Gym and strength training plus everyday, skewed Gen Z.
-Signature proof: Free returns only; leans on cultural content (Gen Z sock debate) instead.</t>
+          <t>Longevity and planetary purpose — 'Built for Years, Not Seasons,' with minimal feature claims.
+Targets: Outdoor and hiking, with everyday crossover
+Signature proof: Guaranteed Quality and profits to the planet</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Tracksmith</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Comfortable, well-made everyday footwear and lifestyle wear with heritage credibility.
-Targets: Everyday wearers, runners, men; back-to-school families.
-Signature proof: Up to 30% off clothing, 25% off shoes, 'Established in 1906', extended widths.</t>
+          <t>Craft running apparel for serious amateurs, anchored in place and pursuit of personal excellence.
+Targets: Runners only (4 of 6 ads)
+Signature proof: 'Designed in Boston' with prices from $54 and no discounting</t>
         </is>
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Patagonia</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Buy once, keep it for years — durability and planet as the value proposition.
-Targets: Outdoor and hiking, plus everyday crossover.
-Signature proof: Guaranteed Quality and profits to the planet.</t>
+          <t>Comfortable everyday footwear and lifestyle heritage; the thinnest message set in the group.
+Targets: Everyday wear, light runner and back-to-school
+Signature proof: Established 1906 craftsmanship plus 30% off promotions</t>
         </is>
       </c>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Alo Yoga</t>
+          <t>Fabletics</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Studio-to-street style with a fashion, celebrity-adjacent sensibility.
-Targets: Everyday athleisure, women and men roughly equally.
-Signature proof: 4.5 rating from 21,131 reviews — the largest review volume in the set.</t>
+          <t>Price disruptor — 'Stop Overpaying for Activewear,' expanding into scrubs and swim via VIP membership.
+Targets: Value seekers, size-inclusive, men's and women's everyday
+Signature proof: $15 first set and 80% off for new VIPs</t>
         </is>
       </c>
     </row>
@@ -751,101 +751,109 @@
     <row r="23">
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Star ratings and review counts (Nike, Alo, Under Armour, Tracksmith, Arc'teryx) — often on tiny sample sizes that undercut the claim</t>
+          <t>Star ratings with review volume — used by 9 of 12 brands, with volume ranging from 22 reviews to 21,615</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Discounts and percentage-off offers (Fabletics, Under Armour, New Balance, Patagonia)</t>
+          <t>Free shipping and generous return windows (30, 60, 120+ days) as a risk-reversal default</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Shipping and returns terms as risk reversal (On, Gymshark, Arc'teryx, Vuori, Tracksmith)</t>
+          <t>Percentage-off promotions and seasonal sale events, often as the ad's lead claim</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Fabric-property lists: breathable, lightweight, sweat-wicking, anti-stink (lululemon, Fabletics, Arc'teryx)</t>
+          <t>Fabric performance descriptors: breathable, lightweight, moisture-wicking, 4-way stretch, anti-stink</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Origin and heritage markers (Designed in Boston, Established 1906, Swiss-engineered)</t>
+          <t>Delivery speed guarantees (1–3, 1–4, 1–5 days)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Named proprietary technology (UA HOVR, Infinion Foam, LightSpray)</t>
+          <t>Guarantees and warranties: Arc'teryx Guarantee, Patagonia Guaranteed Quality, Vuori 100% Product Guarantee</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Named proprietary technology: GORE-TEX ePE, UA HOVR, Infinion Foam, LightSpray</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Heritage and provenance markers: Designed in Boston, Swiss-engineered, Established 1906</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Payment and access incentives: Pay in 4, student discount, VIP membership pricing</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
         <is>
           <t>RECOMMENDATIONS</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="48" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>1.</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Replace generic comfort and performance adjectives with one quantified proof per hero SKU, and lead the ad with it.
-Why: Eleven of twelve brands claim technical performance and the substantiation is almost entirely ratings and shipping terms. A number — grams saved, energy return, wash cycles held, tested moisture rate — is instantly differentiating in an auction where every competing headline says the same thing in different words.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="48" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>2.</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>Claim Community / Belonging as an owned territory with a named program and published participation data.
-Why: It is the emptiest theme in the matrix (two ads total across twelve brands) and the only one that compounds rather than commoditizes. Gymshark treats it as tone of voice, not proof; Tracksmith treats it as heritage. A structured, measurable community gives full-price justification and cuts acquisition cost through member advocacy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="48" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>3.</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>Stop competing on the versatility and comfort keywords where lululemon, Vuori and Fabletics are stacked, and concentrate spend on the under-served audience segments: size-inclusive (one ad, Fabletics only) and yoga/studio (two ads, lululemon and Vuori only).
-Why: Everyday athleisure and versatility are the most saturated intersections in the data, which means the highest bid pressure for the least distinct message. Size-inclusive and studio audiences are commercially large and essentially unaddressed in live creative, so the same budget buys attention instead of parity.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="48" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>4.</t>
+          <t>1.</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Audit and fix low-volume review proof before scaling it.
-Why: Arc'teryx (24 reviews), Tracksmith (22) and Alo's 3.1 store rating actively weaken premium claims. If ratings are the category's default proof, then volume and score are competitive assets — a concentrated review-generation push turns a liability into the one proof point buyers already scan for.</t>
+          <t>Shift the lead message from fabric feel to belonging and provenance. Replace generic comfort/versatility headlines with an identity claim tied to a named group, place, or program, and put membership or participation numbers in the ad as the proof point.
+Why: Comfort and versatility account for the bulk of category ads with near-identical wording, so those claims no longer move preference. Community is claimed by only three brands and provenance by only two — and both Tracksmith and Patagonia use them to hold price while the comfort crowd discounts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="48" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Attach a hard durability or guarantee claim to every ad — a stated lifespan, repair promise, or unconditional guarantee — instead of a percentage-off offer.
+Why: Under Armour, Fabletics and New Balance have made discount depth the price of entry in the value lane, and that is a race no one wins. Arc'teryx, Patagonia and Vuori show guarantees do the same risk-reversal work as a discount without training customers to wait for a sale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="48" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Name and spec one proprietary technology, then run it as a repeatable campaign asset the way On does with LightSpray and UA does with HOVR — specific mechanism, specific benefit, specific number.
+Why: Innovation appears in only 16 ads across the whole set, and On has built runner and outdoor credibility on it while most rivals still say 'breathable' and 'lightweight.' A named, spec'd technology gives sales teams and retail partners something ownable and makes review-count proof secondary rather than the only differentiator.</t>
         </is>
       </c>
     </row>
@@ -934,24 +942,28 @@
         </is>
       </c>
       <c r="B2" s="8" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C2" s="9" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D2" s="9" t="n">
         <v>67</v>
       </c>
       <c r="E2" s="9" t="n">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="F2" s="9" t="n">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="G2" s="10" t="n"/>
-      <c r="H2" s="10" t="n"/>
+      <c r="H2" s="9" t="n">
+        <v>11</v>
+      </c>
       <c r="I2" s="10" t="n"/>
-      <c r="J2" s="10" t="n"/>
+      <c r="J2" s="9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -960,24 +972,24 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C3" s="9" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E3" s="10" t="n"/>
       <c r="F3" s="9" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="H3" s="10" t="n"/>
       <c r="I3" s="9" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J3" s="10" t="n"/>
     </row>
@@ -988,22 +1000,22 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="9" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D4" s="9" t="n">
         <v>100</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="F4" s="9" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="G4" s="9" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="H4" s="9" t="n">
         <v>100</v>
@@ -1018,23 +1030,29 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" s="10" t="n"/>
-      <c r="D5" s="10" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>30</v>
+      </c>
       <c r="E5" s="9" t="n">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G5" s="10" t="n"/>
-      <c r="H5" s="10" t="n"/>
+      <c r="H5" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="I5" s="9" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
@@ -1070,22 +1088,24 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E7" s="9" t="n">
         <v>50</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G7" s="10" t="n"/>
-      <c r="H7" s="10" t="n"/>
+      <c r="H7" s="9" t="n">
+        <v>12</v>
+      </c>
       <c r="I7" s="10" t="n"/>
       <c r="J7" s="10" t="n"/>
     </row>
@@ -1096,24 +1116,28 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="G8" s="10" t="n"/>
-      <c r="H8" s="10" t="n"/>
+        <v>33</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>17</v>
+      </c>
       <c r="I8" s="9" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="J8" s="10" t="n"/>
     </row>
@@ -1174,22 +1198,26 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>100</v>
+        <v>43</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>50</v>
-      </c>
-      <c r="F11" s="10" t="n"/>
+        <v>43</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>29</v>
+      </c>
       <c r="G11" s="10" t="n"/>
-      <c r="H11" s="10" t="n"/>
+      <c r="H11" s="9" t="n">
+        <v>29</v>
+      </c>
       <c r="I11" s="9" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="J11" s="10" t="n"/>
     </row>
@@ -1200,24 +1228,24 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="G12" s="10" t="n"/>
       <c r="H12" s="10" t="n"/>
       <c r="I12" s="9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J12" s="10" t="n"/>
     </row>
@@ -1228,25 +1256,29 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="H13" s="10" t="n"/>
-      <c r="I13" s="10" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="I13" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="J13" s="10" t="n"/>
     </row>
     <row r="14">
@@ -1384,22 +1416,24 @@
         </is>
       </c>
       <c r="B2" s="8" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C2" s="9" t="n">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="D2" s="9" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
+      <c r="F2" s="9" t="n">
+        <v>67</v>
+      </c>
       <c r="G2" s="9" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="H2" s="10" t="n"/>
       <c r="I2" s="9" t="n">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="J2" s="10" t="n"/>
     </row>
@@ -1410,15 +1444,17 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C3" s="9" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="E3" s="10" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>8</v>
+      </c>
       <c r="F3" s="10" t="n"/>
       <c r="G3" s="10" t="n"/>
       <c r="H3" s="9" t="n">
@@ -1434,27 +1470,27 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="9" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="D4" s="9" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E4" s="10" t="n"/>
       <c r="F4" s="10" t="n"/>
       <c r="G4" s="9" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="H4" s="9" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -1464,20 +1500,26 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" s="10" t="n"/>
-      <c r="D5" s="10" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="E5" s="9" t="n">
-        <v>33</v>
-      </c>
-      <c r="F5" s="10" t="n"/>
+        <v>40</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="G5" s="9" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H5" s="10" t="n"/>
       <c r="I5" s="9" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J5" s="10" t="n"/>
     </row>
@@ -1512,20 +1554,26 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>50</v>
-      </c>
-      <c r="D7" s="10" t="n"/>
+        <v>38</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>38</v>
+      </c>
       <c r="E7" s="9" t="n">
-        <v>50</v>
-      </c>
-      <c r="F7" s="10" t="n"/>
-      <c r="G7" s="10" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>25</v>
+      </c>
       <c r="H7" s="10" t="n"/>
       <c r="I7" s="9" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="J7" s="10" t="n"/>
     </row>
@@ -1536,19 +1584,21 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C8" s="10" t="n"/>
-      <c r="D8" s="10" t="n"/>
+      <c r="D8" s="9" t="n">
+        <v>17</v>
+      </c>
       <c r="E8" s="9" t="n">
         <v>50</v>
       </c>
       <c r="F8" s="10" t="n"/>
       <c r="G8" s="9" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="I8" s="9" t="n">
         <v>50</v>
@@ -1608,23 +1658,27 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="F11" s="10" t="n"/>
       <c r="G11" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="H11" s="10" t="n"/>
-      <c r="I11" s="10" t="n"/>
+        <v>71</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>43</v>
+      </c>
       <c r="J11" s="10" t="n"/>
     </row>
     <row r="12">
@@ -1634,28 +1688,28 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J12" s="10" t="n"/>
     </row>
@@ -1666,26 +1720,28 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="H13" s="10" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="I13" s="9" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J13" s="10" t="n"/>
     </row>
@@ -1750,7 +1806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1813,14 +1869,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Arc'teryx</t>
-        </is>
-      </c>
+      <c r="A5" s="14" t="inlineStr"/>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>Rating 4.0 from 24 reviews</t>
+          <t>4.5 rating from 21,615 reviews</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
@@ -1828,14 +1880,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Fabletics</t>
-        </is>
-      </c>
+      <c r="A6" s="14" t="inlineStr"/>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>$19 swimsuits for new VIPs</t>
+          <t>Average delivery time 1 to 4 days</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
@@ -1846,7 +1894,7 @@
       <c r="A7" s="14" t="inlineStr"/>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>50% off Jackets and Vests</t>
+          <t>Celeb-approved</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
@@ -1857,7 +1905,7 @@
       <c r="A8" s="14" t="inlineStr"/>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>50% off Underscrubs</t>
+          <t>Free Shipping and Free Returns</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
@@ -1868,7 +1916,7 @@
       <c r="A9" s="14" t="inlineStr"/>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>80% off everything</t>
+          <t>Free Worldwide Shipping</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
@@ -1879,7 +1927,7 @@
       <c r="A10" s="14" t="inlineStr"/>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>Breathable, lightweight and wrinkle resistant</t>
+          <t>Order accuracy 95 to 100%</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
@@ -1890,7 +1938,7 @@
       <c r="A11" s="14" t="inlineStr"/>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>First Scrub Set for $15</t>
+          <t>Performance-Engineered</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
@@ -1898,14 +1946,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Gymshark</t>
-        </is>
-      </c>
+      <c r="A12" s="14" t="inlineStr"/>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>Free Returns</t>
+          <t>Rating 4.5 from 21,615 reviews</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
@@ -1913,14 +1957,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>New Balance</t>
-        </is>
-      </c>
+      <c r="A13" s="14" t="inlineStr"/>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>25% Off Select Shoes</t>
+          <t>Yogi-Tested</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
@@ -1928,10 +1968,14 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr"/>
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Arc'teryx</t>
+        </is>
+      </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>Up to 30% Off Select Clothing and Accessories</t>
+          <t>Free Shipping and Returns</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
@@ -1939,14 +1983,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
+      <c r="A15" s="14" t="inlineStr"/>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>Average delivery time 1-3 days</t>
+          <t>Gore-tex Jackets</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
@@ -1957,7 +1997,7 @@
       <c r="A16" s="14" t="inlineStr"/>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>Rating 4.7 from 6,660 reviews</t>
+          <t>Insulated Jackets</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
@@ -1965,14 +2005,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>On</t>
-        </is>
-      </c>
+      <c r="A17" s="14" t="inlineStr"/>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>30-day Returns</t>
+          <t>New GORE-TEX ePE Membrane</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
@@ -1983,7 +2019,7 @@
       <c r="A18" s="14" t="inlineStr"/>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>Free Shipping</t>
+          <t>Rating 4.0 from 24 reviews</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
@@ -1991,14 +2027,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Patagonia</t>
-        </is>
-      </c>
+      <c r="A19" s="14" t="inlineStr"/>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>Guaranteed Quality</t>
+          <t>The Arc'teryx Guarantee</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
@@ -2006,10 +2038,14 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr"/>
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Fabletics</t>
+        </is>
+      </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>Up to 40% Off</t>
+          <t>$15 price point</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
@@ -2017,14 +2053,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Tracksmith</t>
-        </is>
-      </c>
+      <c r="A21" s="14" t="inlineStr"/>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>5.0 rating from 22 reviews</t>
+          <t>$19 swimsuits for new VIPs</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
@@ -2035,7 +2067,7 @@
       <c r="A22" s="14" t="inlineStr"/>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>Designed in Boston</t>
+          <t>50% off Jackets and Vests</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
@@ -2046,7 +2078,7 @@
       <c r="A23" s="14" t="inlineStr"/>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>Prices starting from $54.00</t>
+          <t>50% off Underscrubs</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
@@ -2054,14 +2086,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Under Armour</t>
-        </is>
-      </c>
+      <c r="A24" s="14" t="inlineStr"/>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>25% Off BTS Gear</t>
+          <t>80% off everything</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
@@ -2072,7 +2100,7 @@
       <c r="A25" s="14" t="inlineStr"/>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>30-50% Off Sitewide</t>
+          <t>Breathable</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
@@ -2083,7 +2111,7 @@
       <c r="A26" s="14" t="inlineStr"/>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>4.7 rating from 305 reviews</t>
+          <t>Breathable, lightweight and wrinkle resistant</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
@@ -2094,7 +2122,7 @@
       <c r="A27" s="14" t="inlineStr"/>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>Valid Jul 19 to Aug 21</t>
+          <t>First Scrub Set for $15</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
@@ -2102,29 +2130,21 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>Vuori</t>
-        </is>
-      </c>
+      <c r="A28" s="14" t="inlineStr"/>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>(no concrete proof points cited)</t>
+          <t>Lightweight</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>lululemon</t>
-        </is>
-      </c>
+      <c r="A29" s="14" t="inlineStr"/>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>Anti-stink</t>
+          <t>Wrinkle resistant</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
@@ -2132,24 +2152,698 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="14" t="inlineStr"/>
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Gymshark</t>
+        </is>
+      </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>Breathable</t>
+          <t>Free Returns</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr"/>
       <c r="B31" s="14" t="inlineStr">
         <is>
+          <t>4.6 rating from 200 reviews</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr"/>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>Free delivery on orders over $100</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr"/>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>Pay in 4 Installments</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr"/>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>Student Discount</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>New Balance</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>25% Off Select Shoes</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr"/>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>Up to 30% Off Select Clothing and Accessories</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>Average delivery time 1-3 days</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr"/>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>Live Support Available</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr"/>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>Most items returnable 60+ days</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr"/>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>Rating 4.6 from 1,919 reviews</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr"/>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>Rating 4.7 from 6,660 reviews</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>save up to 40%</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr"/>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>30-day Returns</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="inlineStr"/>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>30-day returns</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="inlineStr"/>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>4.6 rating from 58 reviews</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="14" t="inlineStr"/>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>Free Shipping</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="14" t="inlineStr"/>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>Free shipping</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="14" t="inlineStr"/>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>More heel support</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="inlineStr"/>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>New sockliner for easy step-in</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="14" t="inlineStr"/>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>Swiss-engineered</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="14" t="inlineStr"/>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>Wider opening for better fit</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>Patagonia</t>
+        </is>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>Guaranteed Quality</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="14" t="inlineStr"/>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>Up to 40% Off</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>Tracksmith</t>
+        </is>
+      </c>
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>5.0 rating from 22 reviews</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="14" t="inlineStr"/>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>Designed in Boston</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="14" t="inlineStr"/>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>Prices starting from $54.00</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>Under Armour</t>
+        </is>
+      </c>
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>1 to 5 days average delivery time</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="14" t="inlineStr"/>
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t>25% Off BTS Gear</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="14" t="inlineStr"/>
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t>2X A Year</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="14" t="inlineStr"/>
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t>30-50% Off Sitewide</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="14" t="inlineStr"/>
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>4.7 rating from 305 reviews</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="14" t="inlineStr"/>
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>4.8 rating from 221 reviews</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="14" t="inlineStr"/>
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>40% Off Winter Picks</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="14" t="inlineStr"/>
+      <c r="B64" s="14" t="inlineStr">
+        <is>
+          <t>50% Off</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="14" t="inlineStr"/>
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>Rating 4.8 from 305 reviews</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="14" t="inlineStr"/>
+      <c r="B66" s="14" t="inlineStr">
+        <is>
+          <t>Valid Jul 19 to Aug 21</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>Vuori</t>
+        </is>
+      </c>
+      <c r="B67" s="14" t="inlineStr">
+        <is>
+          <t>100% Product Guarantee</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="14" t="inlineStr"/>
+      <c r="B68" s="14" t="inlineStr">
+        <is>
+          <t>120+ days returnable</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="14" t="inlineStr"/>
+      <c r="B69" s="14" t="inlineStr">
+        <is>
+          <t>4-Way Stretch</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="14" t="inlineStr"/>
+      <c r="B70" s="14" t="inlineStr">
+        <is>
+          <t>4.6 rating from 14,413 reviews</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="14" t="inlineStr"/>
+      <c r="B71" s="14" t="inlineStr">
+        <is>
+          <t>Breathable</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="14" t="inlineStr"/>
+      <c r="B72" s="14" t="inlineStr">
+        <is>
+          <t>Free Shipping</t>
+        </is>
+      </c>
+      <c r="C72" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="14" t="inlineStr"/>
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>Free Shipping Over $75</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="14" t="inlineStr"/>
+      <c r="B74" s="14" t="inlineStr">
+        <is>
+          <t>Lightweight and Breathable</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="14" t="inlineStr"/>
+      <c r="B75" s="14" t="inlineStr">
+        <is>
+          <t>Moisture Wicking</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="14" t="inlineStr"/>
+      <c r="B76" s="14" t="inlineStr">
+        <is>
+          <t>Most items returnable 120+ days</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="14" t="inlineStr"/>
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>Rating 4.6 from 13,593 reviews</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>lululemon</t>
+        </is>
+      </c>
+      <c r="B78" s="14" t="inlineStr">
+        <is>
+          <t>25% Off Reduced Shop</t>
+        </is>
+      </c>
+      <c r="C78" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="14" t="inlineStr"/>
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>30+ days returnable</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="14" t="inlineStr"/>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>4.6 advertiser rating</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="14" t="inlineStr"/>
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>4.6 rating from 104 reviews</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="14" t="inlineStr"/>
+      <c r="B82" s="14" t="inlineStr">
+        <is>
+          <t>4.7 rating from 183 reviews</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="14" t="inlineStr"/>
+      <c r="B83" s="14" t="inlineStr">
+        <is>
+          <t>4.7 rating from 185 reviews</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="14" t="inlineStr"/>
+      <c r="B84" s="14" t="inlineStr">
+        <is>
+          <t>Anti-stink</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="14" t="inlineStr"/>
+      <c r="B85" s="14" t="inlineStr">
+        <is>
+          <t>Breathable</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="14" t="inlineStr"/>
+      <c r="B86" s="14" t="inlineStr">
+        <is>
+          <t>Dropping daily</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="14" t="inlineStr"/>
+      <c r="B87" s="14" t="inlineStr">
+        <is>
           <t>Sweat-wicking</t>
         </is>
       </c>
-      <c r="C31" s="8" t="n">
+      <c r="C87" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="14" t="inlineStr"/>
+      <c r="B88" s="14" t="inlineStr">
+        <is>
+          <t>Thousands of gently used items</t>
+        </is>
+      </c>
+      <c r="C88" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="14" t="inlineStr"/>
+      <c r="B89" s="14" t="inlineStr">
+        <is>
+          <t>Women's Gear Under $50</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2164,7 +2858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3870,6 +4564,2336 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>lululemon</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>Shop lululemon Like New - Lululemon Like New. Gently used gear that's just getting started. The official lululemon resale shop is your second chance at past favorites. Sell Online. 25% Off Reduced Shop. Resale Program. Women's Gear Under $50.</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>Promotional</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="inlineStr">
+        <is>
+          <t>Sustainability, Price / Value</t>
+        </is>
+      </c>
+      <c r="E44" s="14" t="inlineStr">
+        <is>
+          <t>Women, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="inlineStr">
+        <is>
+          <t>25% Off Reduced Shop, Women's Gear Under $50</t>
+        </is>
+      </c>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H44" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>lululemon</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>lululemon Like New - New Life For Gently Used Gear. The Like New Resale Shop Is Packed With Thousands of Gently Used Gems, Dropping Daily.</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>Promotional</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr">
+        <is>
+          <t>Sustainability, Price / Value</t>
+        </is>
+      </c>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="F45" s="14" t="inlineStr">
+        <is>
+          <t>Thousands of gently used items, Dropping daily</t>
+        </is>
+      </c>
+      <c r="G45" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H45" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t>lululemon</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>Shop Women's Pants lululemon Like New - The Like New Resale Shop. Packed With Thousands Of Gently Used Gems, Dropping Daily. Pre-Loved Pieces Like This Are Right At Home In The Gym.</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="inlineStr">
+        <is>
+          <t>Sustainability, Price / Value, Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="E46" s="14" t="inlineStr">
+        <is>
+          <t>Women, Gym &amp; strength training</t>
+        </is>
+      </c>
+      <c r="F46" s="14" t="inlineStr"/>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H46" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="14" t="inlineStr">
+        <is>
+          <t>lululemon</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>New Gear Just Dropped - All New Sweatshirts and Hoodies. Soft Sweatshirts Are The Perfect Go-Tos After A Hard Workout. Long, Cropped, Oversized, Slim.</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D47" s="14" t="inlineStr">
+        <is>
+          <t>Comfort / Feel, Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="E47" s="14" t="inlineStr">
+        <is>
+          <t>Women, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="F47" s="14" t="inlineStr"/>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H47" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>lululemon</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>Shop lululemon Scuba Hoodies. Scuba Half Zips Take Comfort To Go, With Naturally Breathable, Soft Fleecy Fabric. Rating 4.7 from 185 reviews. Most items returnable 30+ days.</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr">
+        <is>
+          <t>Comfort / Feel, Style / Design, Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="E48" s="14" t="inlineStr">
+        <is>
+          <t>Women, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="inlineStr">
+        <is>
+          <t>4.7 rating from 185 reviews, 30+ days returnable</t>
+        </is>
+      </c>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H48" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>lululemon</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>Super-Soft Loungewear Is A Go - lululemon Loungewear. Reset And Recharge In Loungewear That Fits Like It's Made For You. Versatile Loungewear That Feels As Good As It Looks.</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="inlineStr">
+        <is>
+          <t>Comfort / Feel</t>
+        </is>
+      </c>
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="inlineStr"/>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H49" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="14" t="inlineStr">
+        <is>
+          <t>lululemon</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>lululemon Official Site - Move In Your Favorite Color. Versatile, Streamlined Sweatpants That Look As Good As They Feel. Men's Bestsellers. Men's Winter Clothes.</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr">
+        <is>
+          <t>Comfort / Feel, Style / Design, Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="E50" s="14" t="inlineStr">
+        <is>
+          <t>Men, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="F50" s="14" t="inlineStr"/>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H50" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t>lululemon</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>You Pick The Length - Shop Men's Underwear. Our Technical Men's Boxers Are Breathable, Roomy, And Come In Different Lengths.</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D51" s="14" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Comfort / Feel, Style / Design, Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="E51" s="14" t="inlineStr">
+        <is>
+          <t>Men</t>
+        </is>
+      </c>
+      <c r="F51" s="14" t="inlineStr"/>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H51" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="14" t="inlineStr">
+        <is>
+          <t>lululemon</t>
+        </is>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>Shop lululemon Golf - Golf Gear, Fit For More. Explore Stretchy, Featherlight Golf Gear Crafted To Keep You, And Your Swing, In Harmony. Ultralight.</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Comfort / Feel, Style / Design, Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="E52" s="14" t="inlineStr">
+        <is>
+          <t>Men, Outdoor &amp; hiking</t>
+        </is>
+      </c>
+      <c r="F52" s="14" t="inlineStr"/>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H52" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="14" t="inlineStr">
+        <is>
+          <t>lululemon</t>
+        </is>
+      </c>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>Women's Golf Clothes - lululemon. Women's run, training, and yoga gear to keep you covered and comfortable no matter how you like to sweat. Rating 4.7 from 183 reviews.</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D53" s="14" t="inlineStr">
+        <is>
+          <t>Comfort / Feel, Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="E53" s="14" t="inlineStr">
+        <is>
+          <t>Women, Runners, Yoga &amp; studio, Gym &amp; strength training</t>
+        </is>
+      </c>
+      <c r="F53" s="14" t="inlineStr">
+        <is>
+          <t>4.7 rating from 183 reviews</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H53" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="14" t="inlineStr">
+        <is>
+          <t>lululemon</t>
+        </is>
+      </c>
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>Sign Up For Early Access - Our Shirts Go Beyond Comfort. T-Shirts This Stretchy and Lightweight Redefine What Comfortable Feels Like. 4.6 advertiser rating.</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D54" s="14" t="inlineStr">
+        <is>
+          <t>Comfort / Feel, Performance / Technical fabric, Innovation / New technology</t>
+        </is>
+      </c>
+      <c r="E54" s="14" t="inlineStr">
+        <is>
+          <t>Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="F54" s="14" t="inlineStr">
+        <is>
+          <t>4.6 advertiser rating</t>
+        </is>
+      </c>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H54" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="14" t="inlineStr">
+        <is>
+          <t>lululemon</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>Women's Vests - Lululemon. Our Technical Vests Offer Warmth Without The Weight, And They Pack Down Small. Rating 4.6 from 104 reviews. We Made Too Much.</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="inlineStr">
+        <is>
+          <t>Comfort / Feel, Performance / Technical fabric</t>
+        </is>
+      </c>
+      <c r="E55" s="14" t="inlineStr">
+        <is>
+          <t>Women, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="F55" s="14" t="inlineStr">
+        <is>
+          <t>4.6 rating from 104 reviews</t>
+        </is>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H55" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="14" t="inlineStr">
+        <is>
+          <t>lululemon</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>Women's Hoodies and Sweatshirts. Versatile Hoodies That Fit Like They're Made For You. Winter Collection Out Now. Free Hemming. Buy Now Pay Later Options.</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D56" s="14" t="inlineStr">
+        <is>
+          <t>Comfort / Feel, Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="E56" s="14" t="inlineStr">
+        <is>
+          <t>Women, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="F56" s="14" t="inlineStr"/>
+      <c r="G56" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H56" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="14" t="inlineStr">
+        <is>
+          <t>lululemon</t>
+        </is>
+      </c>
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>Stretchy Jackets Are A Go - Our Jackets Go Beyond Comfort. Versatile Jackets That Look As Good As They Feel. In Jackets This Lightweight.</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D57" s="14" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Comfort / Feel, Style / Design, Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="E57" s="14" t="inlineStr">
+        <is>
+          <t>Women, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="F57" s="14" t="inlineStr"/>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H57" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="14" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t>Shop Nike Back To School - Nike Men's Activewear. Use promo code DAYONE to get an extra 25% off on select styles. Shop Nike men's apparel for training.</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="inlineStr">
+        <is>
+          <t>Promotional</t>
+        </is>
+      </c>
+      <c r="D58" s="14" t="inlineStr">
+        <is>
+          <t>Price / Value</t>
+        </is>
+      </c>
+      <c r="E58" s="14" t="inlineStr">
+        <is>
+          <t>Men, Gym &amp; strength training</t>
+        </is>
+      </c>
+      <c r="F58" s="14" t="inlineStr"/>
+      <c r="G58" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H58" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="14" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t>Nike - Online Store - The Official Nike Site. Prepare for Matchday and Beyond with Official Nike Football Gear. Gear up for Glory on the Pitch. Click and Collect. Free Delivery For Members. Become A Nike Member.</t>
+        </is>
+      </c>
+      <c r="C59" s="14" t="inlineStr">
+        <is>
+          <t>Promotional</t>
+        </is>
+      </c>
+      <c r="D59" s="14" t="inlineStr">
+        <is>
+          <t>Style / Design, Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="E59" s="14" t="inlineStr">
+        <is>
+          <t>Men</t>
+        </is>
+      </c>
+      <c r="F59" s="14" t="inlineStr"/>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H59" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t>Kids Giannis Antetokounmpo Shoes. Nike.com. Shop The Latest Nike Basketball Styles Designed For Performance. Available On Nike.com.</t>
+        </is>
+      </c>
+      <c r="C60" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D60" s="14" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric</t>
+        </is>
+      </c>
+      <c r="E60" s="14" t="inlineStr">
+        <is>
+          <t>Men, Gym &amp; strength training</t>
+        </is>
+      </c>
+      <c r="F60" s="14" t="inlineStr"/>
+      <c r="G60" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H60" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="14" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>Yoga Shorts. Nike.com. Shop The Official Nike Store For The Latest Nike Shoes, Apparel and Gear. Gear Up For Sport And Style With Nike Products Designed For Performance And Comfort. Live Support Available. Rating 4.6 from 1,919 reviews. Most items returnable 60+ days.</t>
+        </is>
+      </c>
+      <c r="C61" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D61" s="14" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Comfort / Feel, Style / Design</t>
+        </is>
+      </c>
+      <c r="E61" s="14" t="inlineStr">
+        <is>
+          <t>Women, Yoga &amp; studio</t>
+        </is>
+      </c>
+      <c r="F61" s="14" t="inlineStr">
+        <is>
+          <t>Rating 4.6 from 1,919 reviews, Most items returnable 60+ days, Live Support Available</t>
+        </is>
+      </c>
+      <c r="G61" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H61" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="14" t="inlineStr">
+        <is>
+          <t>Vuori</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>Vuori Performance Apparel - Sign Up and Get 20% Off - New Arrivals Are Here. Shop Men's And Women's Performance Apparel. Built To Move In. Styled For Life. 4-Way Stretch. Moisture Wicking. Breathable. 100% Product Guarantee. Free Shipping Over $75. Rating 4.6 from 13,593 reviews. Most items returnable 120+ days.</t>
+        </is>
+      </c>
+      <c r="C62" s="14" t="inlineStr">
+        <is>
+          <t>Promotional</t>
+        </is>
+      </c>
+      <c r="D62" s="14" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Versatility / Gym-to-street, Comfort / Feel</t>
+        </is>
+      </c>
+      <c r="E62" s="14" t="inlineStr">
+        <is>
+          <t>Women, Men</t>
+        </is>
+      </c>
+      <c r="F62" s="14" t="inlineStr">
+        <is>
+          <t>4-Way Stretch, Moisture Wicking, Breathable, 100% Product Guarantee, Free Shipping Over $75, Rating 4.6 from 13,593 reviews, Most items returnable 120+ days</t>
+        </is>
+      </c>
+      <c r="G62" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H62" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="14" t="inlineStr">
+        <is>
+          <t>Vuori</t>
+        </is>
+      </c>
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>Vuori Clothing - Sign Up and Get 20% Off. Vuori Performance Apparel, Built To Move In. Styled For Life. The Tom Holland Edit. Women's Best Sellers. New Arrivals Are Here.</t>
+        </is>
+      </c>
+      <c r="C63" s="14" t="inlineStr">
+        <is>
+          <t>Promotional</t>
+        </is>
+      </c>
+      <c r="D63" s="14" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Style / Design, Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="E63" s="14" t="inlineStr">
+        <is>
+          <t>Women, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="F63" s="14" t="inlineStr"/>
+      <c r="G63" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H63" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="14" t="inlineStr">
+        <is>
+          <t>Vuori</t>
+        </is>
+      </c>
+      <c r="B64" s="14" t="inlineStr">
+        <is>
+          <t>Modern Golf Apparel - Golf Performance Apparel. Thoughtfully Crafted Golf Apparel For Players Who Appreciate Timeless Style And Fit. Shop Vuori Golf And Discover Elevated Apparel You'll Reach For Long. Rating 4.6 from 14,413 reviews. Most items returnable 120+ days.</t>
+        </is>
+      </c>
+      <c r="C64" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="inlineStr">
+        <is>
+          <t>Style / Design, Comfort / Feel, Performance / Technical fabric, Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="E64" s="14" t="inlineStr">
+        <is>
+          <t>Men, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="F64" s="14" t="inlineStr">
+        <is>
+          <t>4.6 rating from 14,413 reviews, 120+ days returnable</t>
+        </is>
+      </c>
+      <c r="G64" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H64" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="14" t="inlineStr">
+        <is>
+          <t>Vuori</t>
+        </is>
+      </c>
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>Sign Up and Get 20% Off - Vuori Official Site. Meet Your New Everyday Clothing. Sign Up With Email and Enjoy 20% Off Your First Purchase. Crafted From The Best.</t>
+        </is>
+      </c>
+      <c r="C65" s="14" t="inlineStr">
+        <is>
+          <t>Promotional</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>Comfort / Feel, Versatility / Gym-to-street, Style / Design, Innovation / New technology</t>
+        </is>
+      </c>
+      <c r="E65" s="14" t="inlineStr">
+        <is>
+          <t>Everyday / athleisure, Women, Men</t>
+        </is>
+      </c>
+      <c r="F65" s="14" t="inlineStr"/>
+      <c r="G65" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H65" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="14" t="inlineStr">
+        <is>
+          <t>Vuori</t>
+        </is>
+      </c>
+      <c r="B66" s="14" t="inlineStr">
+        <is>
+          <t>Official Vuori Site - Men's and Women's Shorts. Vuori Performance Apparel Is Built To Move and Sweat In, Yet Styled For Everyday Life. Designed For Style, Comfort and Performance. Free Shipping. Lightweight and Breathable. New To Vuori?</t>
+        </is>
+      </c>
+      <c r="C66" s="14" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="D66" s="14" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Comfort / Feel, Style / Design, Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="E66" s="14" t="inlineStr">
+        <is>
+          <t>Women, Men, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="F66" s="14" t="inlineStr">
+        <is>
+          <t>Free Shipping, Lightweight and Breathable</t>
+        </is>
+      </c>
+      <c r="G66" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H66" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="14" t="inlineStr">
+        <is>
+          <t>Vuori</t>
+        </is>
+      </c>
+      <c r="B67" s="14" t="inlineStr">
+        <is>
+          <t>Men's and Women's Pants - Official Vuori Site. Crafted From The Best Performance Fabrics and Designed For The Adventurer In All Of Us. Women's Joggers. Men's Signature Joggers. Gym-To-Street Wear.</t>
+        </is>
+      </c>
+      <c r="C67" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D67" s="14" t="inlineStr">
+        <is>
+          <t>Comfort / Feel, Versatility / Gym-to-street, Style / Design</t>
+        </is>
+      </c>
+      <c r="E67" s="14" t="inlineStr">
+        <is>
+          <t>Women, Men, Gym &amp; strength training, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="F67" s="14" t="inlineStr"/>
+      <c r="G67" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H67" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="14" t="inlineStr">
+        <is>
+          <t>Gymshark</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="inlineStr">
+        <is>
+          <t>Your First 5K - Run your first 5K. We'll guide you through every step with an 8-week couch-to-5k training plan, tips from those who've done it, and advice from a coach. 5K Training Plan.</t>
+        </is>
+      </c>
+      <c r="C68" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D68" s="14" t="inlineStr">
+        <is>
+          <t>Innovation / New technology</t>
+        </is>
+      </c>
+      <c r="E68" s="14" t="inlineStr">
+        <is>
+          <t>Runners, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="F68" s="14" t="inlineStr"/>
+      <c r="G68" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H68" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="14" t="inlineStr">
+        <is>
+          <t>Gymshark</t>
+        </is>
+      </c>
+      <c r="B69" s="14" t="inlineStr">
+        <is>
+          <t>How to Train for a Half Marathon From Beginner to Advanced. We share everything you need to include, along with training tips and advice from a Running Coach. New Releases. Student Discount. Pay in 4 Installments. E-Gift Cards. Free Returns. Contactless Delivery.</t>
+        </is>
+      </c>
+      <c r="C69" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D69" s="14" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="E69" s="14" t="inlineStr">
+        <is>
+          <t>Runners</t>
+        </is>
+      </c>
+      <c r="F69" s="14" t="inlineStr"/>
+      <c r="G69" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H69" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="14" t="inlineStr">
+        <is>
+          <t>Gymshark</t>
+        </is>
+      </c>
+      <c r="B70" s="14" t="inlineStr">
+        <is>
+          <t>The Gym Is Everything We Do - Gymshark. Achieve Your Best In and Out Of The Gym With Our High Quality Products and Unrivalled Design.</t>
+        </is>
+      </c>
+      <c r="C70" s="14" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="D70" s="14" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Style / Design, Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="E70" s="14" t="inlineStr">
+        <is>
+          <t>Gym &amp; strength training, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="F70" s="14" t="inlineStr"/>
+      <c r="G70" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H70" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="14" t="inlineStr">
+        <is>
+          <t>Gymshark</t>
+        </is>
+      </c>
+      <c r="B71" s="14" t="inlineStr">
+        <is>
+          <t>Buy Now, Pay Later - Gymshark Gym Clothing. However You Gym, We've Got The Clothes, Accessories and Community For You. Shop Gymshark Gym Apparel. Women's Best Sellers. Sale and Exclusives.</t>
+        </is>
+      </c>
+      <c r="C71" s="14" t="inlineStr">
+        <is>
+          <t>Promotional</t>
+        </is>
+      </c>
+      <c r="D71" s="14" t="inlineStr">
+        <is>
+          <t>Versatility / Gym-to-street, Community / Belonging, Price / Value</t>
+        </is>
+      </c>
+      <c r="E71" s="14" t="inlineStr">
+        <is>
+          <t>Women, Gym &amp; strength training, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="F71" s="14" t="inlineStr"/>
+      <c r="G71" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H71" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="14" t="inlineStr">
+        <is>
+          <t>Gymshark</t>
+        </is>
+      </c>
+      <c r="B72" s="14" t="inlineStr">
+        <is>
+          <t>Men's Workout Shorts and Sport Shorts - Gymshark. Elevate your workout with our high-performance gym shorts. The perfect fusion of style and functionality for superior comfort. Free Delivery available.</t>
+        </is>
+      </c>
+      <c r="C72" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D72" s="14" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Comfort / Feel, Style / Design</t>
+        </is>
+      </c>
+      <c r="E72" s="14" t="inlineStr">
+        <is>
+          <t>Men, Gym &amp; strength training</t>
+        </is>
+      </c>
+      <c r="F72" s="14" t="inlineStr"/>
+      <c r="G72" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H72" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="14" t="inlineStr">
+        <is>
+          <t>Gymshark</t>
+        </is>
+      </c>
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>Gymshark - Official Store - Gym Clothes and Workout Wear. However You Gym, We've Got The Clothes, Accessories and Community For You. Us? Obsessed With The Gym? Yes. Pay in 4 Installments. Student Discount. New Releases. Contactless Delivery.</t>
+        </is>
+      </c>
+      <c r="C73" s="14" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="D73" s="14" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Comfort / Feel, Community / Belonging</t>
+        </is>
+      </c>
+      <c r="E73" s="14" t="inlineStr">
+        <is>
+          <t>Women, Men, Gym &amp; strength training, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="F73" s="14" t="inlineStr"/>
+      <c r="G73" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H73" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="14" t="inlineStr">
+        <is>
+          <t>Gymshark</t>
+        </is>
+      </c>
+      <c r="B74" s="14" t="inlineStr">
+        <is>
+          <t>Gymshark Official Store - Gym Clothes and Workout Clothes. Unlock your full potential with Gymshark workout clothes. Free delivery on orders over $100. E-Gift Cards. Student Discount. New Releases. Free Returns. Pay in 4 Installments. Rating 4.6 from 200 reviews.</t>
+        </is>
+      </c>
+      <c r="C74" s="14" t="inlineStr">
+        <is>
+          <t>Promotional</t>
+        </is>
+      </c>
+      <c r="D74" s="14" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Comfort / Feel, Versatility / Gym-to-street, Price / Value</t>
+        </is>
+      </c>
+      <c r="E74" s="14" t="inlineStr">
+        <is>
+          <t>Gym &amp; strength training, Runners, Yoga &amp; studio, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="F74" s="14" t="inlineStr">
+        <is>
+          <t>Free delivery on orders over $100, Free Returns, 4.6 rating from 200 reviews, Pay in 4 Installments, Student Discount</t>
+        </is>
+      </c>
+      <c r="G74" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H74" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="14" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="B75" s="14" t="inlineStr">
+        <is>
+          <t>On Cyclon Resale - Shop Official Refurbished On Gear. A Second Chance For Every Product.</t>
+        </is>
+      </c>
+      <c r="C75" s="14" t="inlineStr">
+        <is>
+          <t>Promotional</t>
+        </is>
+      </c>
+      <c r="D75" s="14" t="inlineStr">
+        <is>
+          <t>Sustainability, Price / Value</t>
+        </is>
+      </c>
+      <c r="E75" s="14" t="inlineStr">
+        <is>
+          <t>Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="F75" s="14" t="inlineStr"/>
+      <c r="G75" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H75" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="14" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="B76" s="14" t="inlineStr">
+        <is>
+          <t>On Hiking Shoes - On Official Store - With Missiongrip. Hike without pausing your adventure with light, breathable, high-comfort hiking boots. Discover On's hiking boots for those who live for outdoor adventures. Limited editions. Free shipping.</t>
+        </is>
+      </c>
+      <c r="C76" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D76" s="14" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Comfort / Feel, Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="E76" s="14" t="inlineStr">
+        <is>
+          <t>Outdoor &amp; hiking</t>
+        </is>
+      </c>
+      <c r="F76" s="14" t="inlineStr"/>
+      <c r="G76" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H76" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="14" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>On Official Store - Free Shipping. 30-day Returns. The all-day icon, upgraded. Meet the Cloud, designed to keep you going all day. New sockliner for easy step-in, wider opening for a better fit, and more heel support. Rating 4.6 from 58 reviews.</t>
+        </is>
+      </c>
+      <c r="C77" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D77" s="14" t="inlineStr">
+        <is>
+          <t>Comfort / Feel, Versatility / Gym-to-street, Innovation / New technology</t>
+        </is>
+      </c>
+      <c r="E77" s="14" t="inlineStr">
+        <is>
+          <t>Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="F77" s="14" t="inlineStr">
+        <is>
+          <t>4.6 rating from 58 reviews, 30-day returns, Free shipping, New sockliner for easy step-in, Wider opening for better fit, More heel support</t>
+        </is>
+      </c>
+      <c r="G77" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H77" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="14" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="B78" s="14" t="inlineStr">
+        <is>
+          <t>On Official Store - On - Swiss Engineering. Engineered for high performance and complete comfort. Find the right shoe for you. Run on clouds. Men's Collection. All-day sneakers. On's best sellers. Running, Outdoor and All Day.</t>
+        </is>
+      </c>
+      <c r="C78" s="14" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="D78" s="14" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Comfort / Feel, Innovation / New technology</t>
+        </is>
+      </c>
+      <c r="E78" s="14" t="inlineStr">
+        <is>
+          <t>Men, Runners, Outdoor &amp; hiking, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="F78" s="14" t="inlineStr"/>
+      <c r="G78" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H78" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="14" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>Running Shoes and Clothing. Run on clouds with our collection of Swiss-engineered performance running shoes and apparel. Last season: last chance for pieces from previous seasons, save up to 40%. All-day sneakers: unbeatable comfort for the city, travel or everyday exploring.</t>
+        </is>
+      </c>
+      <c r="C79" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D79" s="14" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Comfort / Feel, Versatility / Gym-to-street, Innovation / New technology, Style / Design, Price / Value, Sustainability</t>
+        </is>
+      </c>
+      <c r="E79" s="14" t="inlineStr">
+        <is>
+          <t>Runners, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="F79" s="14" t="inlineStr">
+        <is>
+          <t>Swiss-engineered, save up to 40%</t>
+        </is>
+      </c>
+      <c r="G79" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H79" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="14" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>On Cloudhero Waterproof - Outdoor Shoe For Kids. Rain, puddle or storm, the fully waterproof membrane keeps feet feeling dry and fresh. With an ultra-sticky Missiongrip outsole, so kids can stay sure-footed.</t>
+        </is>
+      </c>
+      <c r="C80" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D80" s="14" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Comfort / Feel, Innovation / New technology</t>
+        </is>
+      </c>
+      <c r="E80" s="14" t="inlineStr">
+        <is>
+          <t>Outdoor &amp; hiking</t>
+        </is>
+      </c>
+      <c r="F80" s="14" t="inlineStr"/>
+      <c r="G80" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H80" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="14" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>Cloudmonster 3 Wide. Triple layer of CloudTec, the maximum iteration of energy return, ready to roll. Speedboard keeps you on pace, from start to finish. Free shipping. 30 days to decide. Limited editions. Free returns. Helion superfoam. Free exchange and returns.</t>
+        </is>
+      </c>
+      <c r="C81" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D81" s="14" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Innovation / New technology</t>
+        </is>
+      </c>
+      <c r="E81" s="14" t="inlineStr">
+        <is>
+          <t>Runners, Gym &amp; strength training</t>
+        </is>
+      </c>
+      <c r="F81" s="14" t="inlineStr"/>
+      <c r="G81" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H81" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="14" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="B82" s="14" t="inlineStr">
+        <is>
+          <t>On Official Store - Running Shoes for Men. Elevate your run with Swiss-engineered performance shoes. Unmatched on feeling and fun. Last season: save up to 40%.</t>
+        </is>
+      </c>
+      <c r="C82" s="14" t="inlineStr">
+        <is>
+          <t>Promotional</t>
+        </is>
+      </c>
+      <c r="D82" s="14" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Innovation / New technology</t>
+        </is>
+      </c>
+      <c r="E82" s="14" t="inlineStr">
+        <is>
+          <t>Men, Runners</t>
+        </is>
+      </c>
+      <c r="F82" s="14" t="inlineStr">
+        <is>
+          <t>save up to 40%</t>
+        </is>
+      </c>
+      <c r="G82" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H82" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="14" t="inlineStr">
+        <is>
+          <t>Alo Yoga</t>
+        </is>
+      </c>
+      <c r="B83" s="14" t="inlineStr">
+        <is>
+          <t>ALO Official Site - Celeb-Favorite Trousers. Ultra-soft, breathable fabrics for full-length support and seamless hold. Go from studio to street.</t>
+        </is>
+      </c>
+      <c r="C83" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D83" s="14" t="inlineStr">
+        <is>
+          <t>Comfort / Feel</t>
+        </is>
+      </c>
+      <c r="E83" s="14" t="inlineStr">
+        <is>
+          <t>Women, Yoga &amp; studio, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="F83" s="14" t="inlineStr"/>
+      <c r="G83" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H83" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="14" t="inlineStr">
+        <is>
+          <t>Alo Yoga</t>
+        </is>
+      </c>
+      <c r="B84" s="14" t="inlineStr">
+        <is>
+          <t>ALO Official Site - Shop ALO Skirts. Celeb-approved tennis skirts, trending for playful, empowered energy. Go from studio to street. Rating 4.5 from 21,615 reviews. Order accuracy 95 to 100%.</t>
+        </is>
+      </c>
+      <c r="C84" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D84" s="14" t="inlineStr">
+        <is>
+          <t>Style / Design, Versatility / Gym-to-street, Community / Belonging</t>
+        </is>
+      </c>
+      <c r="E84" s="14" t="inlineStr">
+        <is>
+          <t>Women, Yoga &amp; studio, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="F84" s="14" t="inlineStr">
+        <is>
+          <t>4.5 rating from 21,615 reviews, Order accuracy 95 to 100%, Celeb-approved</t>
+        </is>
+      </c>
+      <c r="G84" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H84" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="14" t="inlineStr">
+        <is>
+          <t>Alo Yoga</t>
+        </is>
+      </c>
+      <c r="B85" s="14" t="inlineStr">
+        <is>
+          <t>From calm and cool to bold and bright, pick the hue that most matches your mood. Take your practice looks to the pavement with our staple pieces and transitional layers. Join ALO Access. Celeb-Approved. Yogi-Tested.</t>
+        </is>
+      </c>
+      <c r="C85" s="14" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="D85" s="14" t="inlineStr">
+        <is>
+          <t>Style / Design, Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="E85" s="14" t="inlineStr">
+        <is>
+          <t>Women, Yoga &amp; studio, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="F85" s="14" t="inlineStr"/>
+      <c r="G85" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H85" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="14" t="inlineStr">
+        <is>
+          <t>Alo Yoga</t>
+        </is>
+      </c>
+      <c r="B86" s="14" t="inlineStr">
+        <is>
+          <t>Refresh your closet just in time for the new season. Go from studio to street with new leggings, jackets, bras and accessories from ALO. Performance-Engineered. ALO Yoga Workout. Free Worldwide Shipping. Yogi-Tested.</t>
+        </is>
+      </c>
+      <c r="C86" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D86" s="14" t="inlineStr">
+        <is>
+          <t>Comfort / Feel, Style / Design, Versatility / Gym-to-street, Performance / Technical fabric</t>
+        </is>
+      </c>
+      <c r="E86" s="14" t="inlineStr">
+        <is>
+          <t>Women, Yoga &amp; studio, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="F86" s="14" t="inlineStr">
+        <is>
+          <t>Performance-Engineered, Yogi-Tested, Free Worldwide Shipping</t>
+        </is>
+      </c>
+      <c r="G86" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H86" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="14" t="inlineStr">
+        <is>
+          <t>Alo Yoga</t>
+        </is>
+      </c>
+      <c r="B87" s="14" t="inlineStr">
+        <is>
+          <t>ALO Official Site. Go from studio to street with new leggings, jackets, bras and accessories from ALO. Ultra-soft fabrics and studio essentials that fit your body. ALO x Jisoo.</t>
+        </is>
+      </c>
+      <c r="C87" s="14" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="D87" s="14" t="inlineStr">
+        <is>
+          <t>Comfort / Feel, Versatility / Gym-to-street, Style / Design</t>
+        </is>
+      </c>
+      <c r="E87" s="14" t="inlineStr">
+        <is>
+          <t>Women, Yoga &amp; studio, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="F87" s="14" t="inlineStr"/>
+      <c r="G87" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H87" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="14" t="inlineStr">
+        <is>
+          <t>Alo Yoga</t>
+        </is>
+      </c>
+      <c r="B88" s="14" t="inlineStr">
+        <is>
+          <t>ALO Official Site - Bestselling Jackets and Coats - Free Shipping and Free Returns. Rating 4.5 from 21,615 reviews. Average delivery time 1 to 4 days. Men's Best Sellers: top-rated tees, shorts and joggers.</t>
+        </is>
+      </c>
+      <c r="C88" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D88" s="14" t="inlineStr">
+        <is>
+          <t>Comfort / Feel, Versatility / Gym-to-street, Price / Value</t>
+        </is>
+      </c>
+      <c r="E88" s="14" t="inlineStr">
+        <is>
+          <t>Women, Men, Yoga &amp; studio, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="F88" s="14" t="inlineStr">
+        <is>
+          <t>Rating 4.5 from 21,615 reviews, Free Shipping and Free Returns, Average delivery time 1 to 4 days</t>
+        </is>
+      </c>
+      <c r="G88" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H88" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="14" t="inlineStr">
+        <is>
+          <t>Under Armour</t>
+        </is>
+      </c>
+      <c r="B89" s="14" t="inlineStr">
+        <is>
+          <t>50% Off UA - Semi-Annual Event. We Only Do This 2X A Year, You Can't Miss It. Use Code SUMMER Take Up To 50% Off, Just Twice A Year. Grab Fan Favorites At Great Prices.</t>
+        </is>
+      </c>
+      <c r="C89" s="14" t="inlineStr">
+        <is>
+          <t>Promotional</t>
+        </is>
+      </c>
+      <c r="D89" s="14" t="inlineStr"/>
+      <c r="E89" s="14" t="inlineStr">
+        <is>
+          <t>Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="F89" s="14" t="inlineStr">
+        <is>
+          <t>50% Off, 2X A Year</t>
+        </is>
+      </c>
+      <c r="G89" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H89" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="14" t="inlineStr">
+        <is>
+          <t>Under Armour</t>
+        </is>
+      </c>
+      <c r="B90" s="14" t="inlineStr">
+        <is>
+          <t>Under Armour Official Site - Any Workout, Any Weather. Outerwear That Can Handle Anything. Any Sport, Any Condition. Shop UA Outerwear Today. Rating 4.8 from 305 reviews. 40% Off Winter Picks, No Code Needed.</t>
+        </is>
+      </c>
+      <c r="C90" s="14" t="inlineStr">
+        <is>
+          <t>Promotional</t>
+        </is>
+      </c>
+      <c r="D90" s="14" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Versatility / Gym-to-street, Style / Design</t>
+        </is>
+      </c>
+      <c r="E90" s="14" t="inlineStr">
+        <is>
+          <t>Women, Men, Runners, Gym &amp; strength training, Outdoor &amp; hiking</t>
+        </is>
+      </c>
+      <c r="F90" s="14" t="inlineStr">
+        <is>
+          <t>Rating 4.8 from 305 reviews, 40% Off Winter Picks</t>
+        </is>
+      </c>
+      <c r="G90" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H90" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="14" t="inlineStr">
+        <is>
+          <t>Under Armour</t>
+        </is>
+      </c>
+      <c r="B91" s="14" t="inlineStr">
+        <is>
+          <t>Under Armour Golf Shirts - Shop UA Golf Shirts. Experience Superior Comfort and Durability. Get The Gear Everyone's After. New Styles Available.</t>
+        </is>
+      </c>
+      <c r="C91" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D91" s="14" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Comfort / Feel</t>
+        </is>
+      </c>
+      <c r="E91" s="14" t="inlineStr">
+        <is>
+          <t>Men</t>
+        </is>
+      </c>
+      <c r="F91" s="14" t="inlineStr"/>
+      <c r="G91" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H91" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="14" t="inlineStr">
+        <is>
+          <t>Under Armour</t>
+        </is>
+      </c>
+      <c r="B92" s="14" t="inlineStr">
+        <is>
+          <t>Under Armour Official Site - Shop The Official Site. Get The Gear Everyone's After. Shop Under Armour Workout Tees Today. Everything You Need. Nothing You Don't. Largest Style Selection. Pace Your Payments. Rating 4.8 from 221 reviews. Average delivery time 1 to 5 days.</t>
+        </is>
+      </c>
+      <c r="C92" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D92" s="14" t="inlineStr">
+        <is>
+          <t>Style / Design, Versatility / Gym-to-street, Price / Value</t>
+        </is>
+      </c>
+      <c r="E92" s="14" t="inlineStr">
+        <is>
+          <t>Women, Men, Gym &amp; strength training, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="F92" s="14" t="inlineStr">
+        <is>
+          <t>4.8 rating from 221 reviews, 1 to 5 days average delivery time</t>
+        </is>
+      </c>
+      <c r="G92" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H92" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="14" t="inlineStr">
+        <is>
+          <t>Under Armour</t>
+        </is>
+      </c>
+      <c r="B93" s="14" t="inlineStr">
+        <is>
+          <t>Start Strong, Get Stronger - UA MK-1 Collection. Grab Deals on Shoes, Shorts, Ts and More. No Code Needed At Checkout. US and CA Only.</t>
+        </is>
+      </c>
+      <c r="C93" s="14" t="inlineStr">
+        <is>
+          <t>Promotional</t>
+        </is>
+      </c>
+      <c r="D93" s="14" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Price / Value</t>
+        </is>
+      </c>
+      <c r="E93" s="14" t="inlineStr">
+        <is>
+          <t>Gym &amp; strength training, Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="F93" s="14" t="inlineStr"/>
+      <c r="G93" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H93" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="14" t="inlineStr">
+        <is>
+          <t>Arc'teryx</t>
+        </is>
+      </c>
+      <c r="B94" s="14" t="inlineStr">
+        <is>
+          <t>Outdoor Clothing, Technical Outerwear and Accessories - Arc'teryx United States. Arc'teryx is a high performance outdoor equipment company known for leading innovations in climbing, skiing and alpine technologies. Women's Collection. Men's Collection. Women's Jacket Finder.</t>
+        </is>
+      </c>
+      <c r="C94" s="14" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="D94" s="14" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Innovation / New technology</t>
+        </is>
+      </c>
+      <c r="E94" s="14" t="inlineStr">
+        <is>
+          <t>Women, Men, Outdoor &amp; hiking</t>
+        </is>
+      </c>
+      <c r="F94" s="14" t="inlineStr"/>
+      <c r="G94" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H94" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="14" t="inlineStr">
+        <is>
+          <t>Arc'teryx</t>
+        </is>
+      </c>
+      <c r="B95" s="14" t="inlineStr">
+        <is>
+          <t>Arc'teryx Outerwear - Free shipping and free returns - Field-tested protection. In the mountains, having the right gear matters: shells, belay jackets, footwear and more. Hiking and trekking. Gifts For Him. Gifts For Her.</t>
+        </is>
+      </c>
+      <c r="C95" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D95" s="14" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric</t>
+        </is>
+      </c>
+      <c r="E95" s="14" t="inlineStr">
+        <is>
+          <t>Outdoor &amp; hiking, Women, Men</t>
+        </is>
+      </c>
+      <c r="F95" s="14" t="inlineStr"/>
+      <c r="G95" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H95" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="14" t="inlineStr">
+        <is>
+          <t>Arc'teryx</t>
+        </is>
+      </c>
+      <c r="B96" s="14" t="inlineStr">
+        <is>
+          <t>High-performance gear. Stay on the move with packable layers and lightweight fabrics. Trail-ready gear combining packability and protection. High-Performance Apparel. Versatile Designs. Skiing and Snowboarding. Men's Climbing Clothes and Accessories.</t>
+        </is>
+      </c>
+      <c r="C96" s="14" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="D96" s="14" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="E96" s="14" t="inlineStr">
+        <is>
+          <t>Outdoor &amp; hiking, Runners</t>
+        </is>
+      </c>
+      <c r="F96" s="14" t="inlineStr"/>
+      <c r="G96" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H96" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="14" t="inlineStr">
+        <is>
+          <t>Arc'teryx</t>
+        </is>
+      </c>
+      <c r="B97" s="14" t="inlineStr">
+        <is>
+          <t>All-Weather Essentials - Stay Comfortable All Day. Designed for mixed-weather, these durable pieces deliver all-day comfort and protection. Men's Best Sellers. Gore-tex Jackets. Insulated Jackets. New GORE-TEX ePE Membrane.</t>
+        </is>
+      </c>
+      <c r="C97" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D97" s="14" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Comfort / Feel</t>
+        </is>
+      </c>
+      <c r="E97" s="14" t="inlineStr">
+        <is>
+          <t>Men, Outdoor &amp; hiking</t>
+        </is>
+      </c>
+      <c r="F97" s="14" t="inlineStr">
+        <is>
+          <t>Gore-tex Jackets, Insulated Jackets, New GORE-TEX ePE Membrane</t>
+        </is>
+      </c>
+      <c r="G97" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H97" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="14" t="inlineStr">
+        <is>
+          <t>Arc'teryx</t>
+        </is>
+      </c>
+      <c r="B98" s="14" t="inlineStr">
+        <is>
+          <t>Hiking and trekking - Sun protection collection 2026 - Multi-day comfort. Stay on the move with packable layers and lightweight fabrics. Trail-ready gear combining packability and protection. Best-In-Class Equipment.</t>
+        </is>
+      </c>
+      <c r="C98" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D98" s="14" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Comfort / Feel, Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="E98" s="14" t="inlineStr">
+        <is>
+          <t>Outdoor &amp; hiking</t>
+        </is>
+      </c>
+      <c r="F98" s="14" t="inlineStr"/>
+      <c r="G98" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H98" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="14" t="inlineStr">
+        <is>
+          <t>Arc'teryx</t>
+        </is>
+      </c>
+      <c r="B99" s="14" t="inlineStr">
+        <is>
+          <t>Shop Arc'teryx Nuclei - Made for Mountain Athletes. Durable, breathable weather protection, built for everything you don't plan. Skiing and Snowboarding. Women's Jacket Finder.</t>
+        </is>
+      </c>
+      <c r="C99" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D99" s="14" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Comfort / Feel, Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="E99" s="14" t="inlineStr">
+        <is>
+          <t>Women, Outdoor &amp; hiking</t>
+        </is>
+      </c>
+      <c r="F99" s="14" t="inlineStr"/>
+      <c r="G99" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H99" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="14" t="inlineStr">
+        <is>
+          <t>Arc'teryx</t>
+        </is>
+      </c>
+      <c r="B100" s="14" t="inlineStr">
+        <is>
+          <t>Arc'teryx Outerwear - Sun protection gear is here. Our lightweight layers are designed to keep you cool, covered, and protected from UV rays. Trail-ready gear.</t>
+        </is>
+      </c>
+      <c r="C100" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D100" s="14" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Comfort / Feel</t>
+        </is>
+      </c>
+      <c r="E100" s="14" t="inlineStr">
+        <is>
+          <t>Outdoor &amp; hiking</t>
+        </is>
+      </c>
+      <c r="F100" s="14" t="inlineStr"/>
+      <c r="G100" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H100" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="14" t="inlineStr">
+        <is>
+          <t>Arc'teryx</t>
+        </is>
+      </c>
+      <c r="B101" s="14" t="inlineStr">
+        <is>
+          <t>Arc'teryx Men's Clothing - Hot-weather gear. Protect your skin with Arc'teryx men's sun protective clothing collection. Trail-ready gear combining packability and protection. High-Performance Apparel. Female-Specific Designs. Free Shipping and Returns. Versatile Designs. The Arc'teryx Guarantee.</t>
+        </is>
+      </c>
+      <c r="C101" s="14" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D101" s="14" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Comfort / Feel, Versatility / Gym-to-street</t>
+        </is>
+      </c>
+      <c r="E101" s="14" t="inlineStr">
+        <is>
+          <t>Men, Outdoor &amp; hiking</t>
+        </is>
+      </c>
+      <c r="F101" s="14" t="inlineStr">
+        <is>
+          <t>Free Shipping and Returns, The Arc'teryx Guarantee</t>
+        </is>
+      </c>
+      <c r="G101" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H101" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="14" t="inlineStr">
+        <is>
+          <t>Fabletics</t>
+        </is>
+      </c>
+      <c r="B102" s="14" t="inlineStr">
+        <is>
+          <t>First Scrub Set for $15 - Purple Scrub Sets In Stock. Our scrub sets are breathable, lightweight and wrinkle resistant. $15 for new Fabletics VIPs. Exclusive Access: New VIPs Get Your First Activewear Scrub Set for $15.</t>
+        </is>
+      </c>
+      <c r="C102" s="14" t="inlineStr">
+        <is>
+          <t>Promotional</t>
+        </is>
+      </c>
+      <c r="D102" s="14" t="inlineStr">
+        <is>
+          <t>Performance / Technical fabric, Comfort / Feel, Price / Value</t>
+        </is>
+      </c>
+      <c r="E102" s="14" t="inlineStr">
+        <is>
+          <t>Everyday / athleisure</t>
+        </is>
+      </c>
+      <c r="F102" s="14" t="inlineStr">
+        <is>
+          <t>Breathable, Lightweight, Wrinkle resistant, $15 price point</t>
+        </is>
+      </c>
+      <c r="G102" s="14" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="H102" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/messaging_matrix.xlsx
+++ b/output/messaging_matrix.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Findings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Messaging Matrix" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Audience Matrix" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Proof Points" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Tagged Ads" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Messaging Matrix" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audience Matrix" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proof Points" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tagged Ads" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -519,7 +519,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Every brand in the category is selling comfort, versatility and technical performance in nearly identical language — the only genuinely under-claimed territories are community/belonging (5 ads across 3 brands) and durability/sustainability, which means differentiation now comes from proof, not adjectives.</t>
+          <t>Comfort and gym-to-street versatility have become the category's default message — lululemon and Vuori already own it — while community, sustainability and durability sit almost entirely unclaimed, and nearly every brand is defending price with discounts rather than proof.</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Community and identity are the least crowded themes: only Gymshark (3), Alo (1) and Tracksmith (1) make any belonging claim, and only Gymshark ties it to a real subculture. Sustainability is similarly thin (lululemon 4, On 2, everyone else 0–1) and is currently claimed as a compliance footnote rather than a reason to buy. Meanwhile 'comfort' and 'gym-to-street versatility' carry roughly 70 of the ads in this set with interchangeable copy — 'buttery-soft,' 'built to move in, styled for life,' 'looks as good as it feels.'</t>
+          <t>Community and belonging is the least crowded theme in the set: just 6 ads across 12 brands, 5 of them Gymshark's, and Gymshark frames it narrowly around the weight room ('However You Gym, We've Got The Clothes, Accessories and Community'). Sustainability is equally thin (7 ads total, and Patagonia — the brand that should own it — is running only one), but it converts poorly as a lead message. Community is the open lane with commercial teeth.</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Undifferentiated comfort/versatility claims force competition on discount depth, which is exactly where Under Armour (50% off, 30–50% off sitewide), Fabletics ($15 sets, 80% off) and New Balance (30% off) already live. Ads anchored in identity and provenance defend full price: Tracksmith holds a $54 floor on 'Designed in Boston,' and Patagonia sells on 'Built for Years, Not Seasons' with almost no feature copy at all. Belonging also compounds — it drives repeat purchase and organic content rather than one-time conversion.</t>
+          <t>Every brand here is selling the same buttery-soft, do-it-all product story into the same 'everyday / athleisure' audience — lululemon (13 ads), Vuori (9), Gymshark (8), Alo (8). When product claims converge, the only durable differentiator is why someone stays with the brand. Community messaging drives repeat purchase and referral, which is the cheapest growth available when paid acquisition is a bidding war against Nike and lululemon budgets. It also gives you something competitors cannot copy in a quarter: Under Armour can match a 50% discount overnight; it cannot match a 40,000-member run club.</t>
         </is>
       </c>
     </row>
@@ -562,7 +562,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Build a campaign line around who the customer is and what they belong to, not how the fabric feels — a named crew, level, or place (city runs, lifting groups, a training program) with member proof in the ad unit: participation numbers, meetup cadence, user-submitted results. Pair it with a durability guarantee claim ('built for X years' or a lifetime repair promise) so the identity story has a hard commercial fact attached and the ad stops competing on softness.</t>
+          <t>Build a named, ownable membership layer and put it in the ad copy, not just the loyalty email. Lead with countable social proof — number of members, weekly meetups, cities, events completed — the same way rivals lead with review counts. Anchor it to a specific ritual (a weekly run, a lift series, a race team) rather than a vague 'community' claim, and run the ads against the everyday/athleisure audience where the product message is most commoditized.</t>
         </is>
       </c>
     </row>
@@ -581,163 +581,163 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>The default all-day wardrobe — one garment that runs, trains, flows and relaxes, with the broadest claim set in the category.
-Targets: Women and everyday athleisure buyers above all (12 women, 13 everyday ads)
-Signature proof: Functional triad: sweat-wicking, breathable, anti-stink</t>
+          <t>The category default: maximum comfort in clothing engineered to move from workout to the rest of the day.
+Targets: Women (12 ads) and the everyday/athleisure buyer (13) above all else
+Signature proof: 4.7 rating from 185 reviews plus 30+ day returns, backed by 'Women's Gear Under $50' price anchors</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vuori</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Generic sport-and-style authority; ads lean on store credibility rather than a distinct product argument.
-Targets: Split evenly across women, men, runners and gym; no clear focus
-Signature proof: 4.7 rating from 6,660 reviews and 1–3 day delivery</t>
+          <t>Premium performance apparel that refuses to trade comfort or style for technicality — 'Built To Move In. Styled For Life.'
+Targets: The most gender-balanced book in the set: women (8), men (7), everyday/athleisure (9)
+Signature proof: 4.6 rating from 14,413 reviews, 120+ day returns and a 100% Product Guarantee</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Alo Yoga</t>
+          <t>On</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Studio-to-street fashion activewear with celebrity social proof standing in for performance evidence.
-Targets: Women, yoga/studio and everyday athleisure
-Signature proof: 4.5 rating from 21,615 reviews plus 'Celeb-approved'</t>
+          <t>Swiss engineering and visible innovation — cushioning, LightSpray, waterproofing — as the reason to run and walk in On.
+Targets: Runners (7), everyday/athleisure (6), outdoor &amp; hiking (4)
+Signature proof: Named proprietary technology (Cloudboom, LightSpray) plus 30-day returns and free shipping</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Vuori</t>
+          <t>Arc'teryx</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Premium performance apparel that refuses to sacrifice comfort — the most style-forward technical claim in the set.
-Targets: Balanced men and women, heavily everyday/athleisure
-Signature proof: 120+ day returns and 4.6 from 14,413 reviews</t>
+          <t>The most technically uncompromising brand here: performance apparel for hard days outside, with almost no lifestyle softening.
+Targets: Outdoor &amp; hiking (12 ads) — the deepest single-audience focus in the set
+Signature proof: The Arc'teryx Guarantee</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>On</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Swiss-engineered innovation — the only brand where new technology is a lead message, not a footnote (8 innovation ads).
-Targets: Runners, outdoor and everyday sneaker buyers
-Signature proof: Named engineering detail: LightSpray upper, new sockliner, Swiss-engineered</t>
+          <t>The generalist incumbent: sport, style and comfort across every category, sold on brand and breadth.
+Targets: Spread thin — women (3), men (2), one ad each across runners, yoga, gym, everyday
+Signature proof: 4.7 rating from 6,660 reviews, 1-3 day delivery, 60+ day returns</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Under Armour</t>
+          <t>Gymshark</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Performance tech sold through discount urgency; the promotion is the headline.
-Targets: Gym and strength training, men skewed
-Signature proof: '50% Off, 2X A Year' semi-annual event</t>
+          <t>'We Do Gym' — training-first apparel wrapped in a Gen Z culture and community identity.
+Targets: Gym &amp; strength training (7) and everyday/athleisure (8), with a young, content-native tone
+Signature proof: Community itself, supported by free delivery over $100 and Pay in 4 installments</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Gymshark</t>
+          <t>Under Armour</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Gym culture as identity — 'We Do Gym' plus community and content, not just clothing.
-Targets: Gym and strength training, everyday wear, plus a growing runner push
-Signature proof: Community-led editorial content and Pay in 4 / student discount access</t>
+          <t>Performance tech sold almost entirely on promotion — the discount brand of the premium set.
+Targets: Gym &amp; strength training (5), men (4), everyday (3), women (3)
+Signature proof: 30-50% off sitewide and the '2X A Year' Semi-Annual Event, plus 4.8 rating from 305 reviews</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Arc'teryx</t>
+          <t>Alo Yoga</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Uncompromising technical outerwear for real mountain conditions — the purest performance play (11 of 20 ads).
-Targets: Outdoor and hiking almost exclusively (12 ads)
-Signature proof: GORE-TEX ePE membrane and The Arc'teryx Guarantee</t>
+          <t>Studio-to-street style: celeb-adjacent, fashion-forward pieces that happen to be activewear.
+Targets: Women (7), everyday/athleisure (8), yoga &amp; studio (6)
+Signature proof: 4.5 rating from 21,615 reviews and 30+ day returns</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Patagonia</t>
+          <t>Fabletics</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Longevity and planetary purpose — 'Built for Years, Not Seasons,' with minimal feature claims.
-Targets: Outdoor and hiking, with everyday crossover
-Signature proof: Guaranteed Quality and profits to the planet</t>
+          <t>'Stop Overpaying for Activewear' — VIP membership pricing as the entire proposition, now extended into scrubs and swim.
+Targets: Deal-seeking women and men in everyday wear; the only brand with a size-inclusive ad
+Signature proof: $15 first set and 80% off for new VIPs</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Tracksmith</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Craft running apparel for serious amateurs, anchored in place and pursuit of personal excellence.
-Targets: Runners only (4 of 6 ads)
-Signature proof: 'Designed in Boston' with prices from $54 and no discounting</t>
+          <t>Heritage craftsmanship and everyday comfort footwear — lifestyle first, running second.
+Targets: Everyday/athleisure (3), with light runner and men's targeting
+Signature proof: Up to 30% off apparel, 25% off shoes; 'Established In 1906'</t>
         </is>
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Tracksmith</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Comfortable everyday footwear and lifestyle heritage; the thinnest message set in the group.
-Targets: Everyday wear, light runner and back-to-school
-Signature proof: Established 1906 craftsmanship plus 30% off promotions</t>
+          <t>Boston-designed running apparel for serious amateurs pursuing personal excellence — the specialist's brand.
+Targets: Runners (4), and essentially no one else
+Signature proof: 5.0 rating from 22 reviews and transparent pricing from $54</t>
         </is>
       </c>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Fabletics</t>
+          <t>Patagonia</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Price disruptor — 'Stop Overpaying for Activewear,' expanding into scrubs and swim via VIP membership.
-Targets: Value seekers, size-inclusive, men's and women's everyday
-Signature proof: $15 first set and 80% off for new VIPs</t>
+          <t>'Built for Years, Not Seasons' — durability and planetary purpose over performance specs.
+Targets: Outdoor &amp; hiking (3) and everyday (2), on a very small ad footprint
+Signature proof: Guaranteed Quality and 'Profits Go to the Planet'</t>
         </is>
       </c>
     </row>
@@ -751,109 +751,95 @@
     <row r="23">
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Star ratings with review volume — used by 9 of 12 brands, with volume ranging from 22 reviews to 21,615</t>
+          <t>Star ratings paired with review volume — the near-universal trust signal, ranging from Vuori's 14,413 reviews to Arc'teryx's 24</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Free shipping and generous return windows (30, 60, 120+ days) as a risk-reversal default</t>
+          <t>Discount depth as a headline: 25-50% off at Under Armour, New Balance, lululemon, On and Patagonia; 80% off at Fabletics</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Percentage-off promotions and seasonal sale events, often as the ad's lead claim</t>
+          <t>Return windows as risk reversal — Vuori's 120+ days, Nike's 60+, lululemon and Alo at 30+, On at 30</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Fabric performance descriptors: breathable, lightweight, moisture-wicking, 4-way stretch, anti-stink</t>
+          <t>Free shipping thresholds ($75 Vuori, $100 Gymshark, $150 Tracksmith) and stated delivery speed (1-3 days Nike, 1-4 days Alo)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Delivery speed guarantees (1–3, 1–4, 1–5 days)</t>
+          <t>Lifetime or product guarantees as durability shorthand — the Arc'teryx Guarantee, Vuori's 100% Product Guarantee, Patagonia's Guaranteed Quality</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Guarantees and warranties: Arc'teryx Guarantee, Patagonia Guaranteed Quality, Vuori 100% Product Guarantee</t>
+          <t>Payment and membership mechanics — Gymshark's Pay in 4, Fabletics' VIP tier, UA Rewards</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Named proprietary technology: GORE-TEX ePE, UA HOVR, Infinion Foam, LightSpray</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>Heritage and provenance markers: Designed in Boston, Swiss-engineered, Established 1906</t>
+          <t>Named proprietary technology as performance evidence — UA HOVR, On LightSpray, New Balance Infinion Foam</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Payment and access incentives: Pay in 4, student discount, VIP membership pricing</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t>RECOMMENDATIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>1.</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Stake a claim on community with countable proof, and run it against the everyday/athleisure audience rather than the gym.
+Why: Only Gymshark is meaningfully in this space and only in a training context, leaving the largest audience segment in the category — everyday/athleisure, where lululemon, Vuori, Alo and Gymshark are all crowded onto identical comfort and versatility claims — with no belonging story attached to it. Publish membership numbers, event counts and city coverage in ad copy the way rivals publish review counts; it is the one proof point competitors cannot replicate with a markdown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Replace discount-led value messaging with a longevity guarantee and a long return window.
+Why: Price is contested by everyone but the floor is already set by Under Armour's 50% semi-annual event and Fabletics' $15 VIP entry — you cannot win that fight and margin at the same time. Vuori's 120+ day returns and Patagonia's 'Built for Years, Not Seasons' show the alternative: value expressed as cost-per-wear and risk removal. Durability is barely claimed by anyone else, and it justifies premium pricing instead of eroding it.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="48" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>1.</t>
+          <t>3.</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Shift the lead message from fabric feel to belonging and provenance. Replace generic comfort/versatility headlines with an identity claim tied to a named group, place, or program, and put membership or participation numbers in the ad as the proof point.
-Why: Comfort and versatility account for the bulk of category ads with near-identical wording, so those claims no longer move preference. Community is claimed by only three brands and provenance by only two — and both Tracksmith and Patagonia use them to hold price while the comfort crowd discounts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="48" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>2.</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>Attach a hard durability or guarantee claim to every ad — a stated lifespan, repair promise, or unconditional guarantee — instead of a percentage-off offer.
-Why: Under Armour, Fabletics and New Balance have made discount depth the price of entry in the value lane, and that is a race no one wins. Arc'teryx, Patagonia and Vuori show guarantees do the same risk-reversal work as a discount without training customers to wait for a sale.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="48" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>3.</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>Name and spec one proprietary technology, then run it as a repeatable campaign asset the way On does with LightSpray and UA does with HOVR — specific mechanism, specific benefit, specific number.
-Why: Innovation appears in only 16 ads across the whole set, and On has built runner and outdoor credibility on it while most rivals still say 'breathable' and 'lightweight.' A named, spec'd technology gives sales teams and retail partners something ownable and makes review-count proof secondary rather than the only differentiator.</t>
+          <t>Own women in strength training and size-inclusive fit as a named audience.
+Why: lululemon dominates women (12 ads) but almost entirely through everyday and comfort framing; Gymshark owns gym and strength (7 ads) but runs only 2 women's ads; and size-inclusivity appears exactly once in the entire matrix, from Fabletics. That intersection is a real, growing buyer with no dedicated advertiser. Build product proof around fit range and load-bearing performance, and target it directly rather than adding it as a footnote to a general women's campaign.</t>
         </is>
       </c>
     </row>
@@ -982,7 +968,7 @@
       </c>
       <c r="E3" s="10" t="n"/>
       <c r="F3" s="9" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G3" s="9" t="n">
         <v>8</v>
@@ -1014,9 +1000,7 @@
       <c r="F4" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="G4" s="9" t="n">
-        <v>25</v>
-      </c>
+      <c r="G4" s="10" t="n"/>
       <c r="H4" s="9" t="n">
         <v>100</v>
       </c>
@@ -1046,13 +1030,13 @@
       </c>
       <c r="G5" s="10" t="n"/>
       <c r="H5" s="9" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
@@ -1077,7 +1061,9 @@
         <v>50</v>
       </c>
       <c r="G6" s="10" t="n"/>
-      <c r="H6" s="10" t="n"/>
+      <c r="H6" s="9" t="n">
+        <v>25</v>
+      </c>
       <c r="I6" s="10" t="n"/>
       <c r="J6" s="10" t="n"/>
     </row>
@@ -1125,16 +1111,16 @@
         <v>67</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>33</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I8" s="9" t="n">
         <v>67</v>
@@ -1156,12 +1142,14 @@
       <c r="D9" s="10" t="n"/>
       <c r="E9" s="10" t="n"/>
       <c r="F9" s="9" t="n">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="H9" s="10" t="n"/>
+      <c r="H9" s="9" t="n">
+        <v>33</v>
+      </c>
       <c r="I9" s="10" t="n"/>
       <c r="J9" s="10" t="n"/>
     </row>
@@ -1185,11 +1173,11 @@
       </c>
       <c r="F10" s="10" t="n"/>
       <c r="G10" s="10" t="n"/>
-      <c r="H10" s="10" t="n"/>
+      <c r="H10" s="9" t="n">
+        <v>75</v>
+      </c>
       <c r="I10" s="10" t="n"/>
-      <c r="J10" s="9" t="n">
-        <v>25</v>
-      </c>
+      <c r="J10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -1214,7 +1202,7 @@
       </c>
       <c r="G11" s="10" t="n"/>
       <c r="H11" s="9" t="n">
-        <v>29</v>
+        <v>86</v>
       </c>
       <c r="I11" s="9" t="n">
         <v>14</v>
@@ -1243,9 +1231,11 @@
         <v>90</v>
       </c>
       <c r="G12" s="10" t="n"/>
-      <c r="H12" s="10" t="n"/>
+      <c r="H12" s="9" t="n">
+        <v>50</v>
+      </c>
       <c r="I12" s="9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J12" s="10" t="n"/>
     </row>
@@ -1274,7 +1264,7 @@
         <v>22</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="I13" s="9" t="n">
         <v>6</v>
@@ -1452,9 +1442,7 @@
       <c r="D3" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="E3" s="9" t="n">
-        <v>8</v>
-      </c>
+      <c r="E3" s="10" t="n"/>
       <c r="F3" s="10" t="n"/>
       <c r="G3" s="10" t="n"/>
       <c r="H3" s="9" t="n">
@@ -1560,16 +1548,16 @@
         <v>38</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>12</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="H7" s="10" t="n"/>
       <c r="I7" s="9" t="n">
@@ -1591,11 +1579,11 @@
         <v>17</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F8" s="10" t="n"/>
       <c r="G8" s="9" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H8" s="9" t="n">
         <v>33</v>
@@ -1806,7 +1794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C89"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1894,7 +1882,7 @@
       <c r="A7" s="14" t="inlineStr"/>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>Celeb-approved</t>
+          <t>Order accuracy 95 to 100%</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
@@ -1905,7 +1893,7 @@
       <c r="A8" s="14" t="inlineStr"/>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>Free Shipping and Free Returns</t>
+          <t>Rating 4.5 from 21,615 reviews</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
@@ -1913,10 +1901,14 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr"/>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Arc'teryx</t>
+        </is>
+      </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>Free Worldwide Shipping</t>
+          <t>Rating 4.0 from 24 reviews</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
@@ -1927,7 +1919,7 @@
       <c r="A10" s="14" t="inlineStr"/>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>Order accuracy 95 to 100%</t>
+          <t>The Arc'teryx Guarantee</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
@@ -1935,10 +1927,14 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr"/>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Fabletics</t>
+        </is>
+      </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>Performance-Engineered</t>
+          <t>$15 price point</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
@@ -1949,7 +1945,7 @@
       <c r="A12" s="14" t="inlineStr"/>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>Rating 4.5 from 21,615 reviews</t>
+          <t>$19 swimsuits for new VIPs</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
@@ -1960,7 +1956,7 @@
       <c r="A13" s="14" t="inlineStr"/>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>Yogi-Tested</t>
+          <t>50% off Jackets and Vests</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
@@ -1968,14 +1964,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Arc'teryx</t>
-        </is>
-      </c>
+      <c r="A14" s="14" t="inlineStr"/>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>Free Shipping and Returns</t>
+          <t>50% off Underscrubs</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
@@ -1986,7 +1978,7 @@
       <c r="A15" s="14" t="inlineStr"/>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>Gore-tex Jackets</t>
+          <t>80% off everything</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
@@ -1997,7 +1989,7 @@
       <c r="A16" s="14" t="inlineStr"/>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>Insulated Jackets</t>
+          <t>First Scrub Set for $15</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
@@ -2005,10 +1997,14 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr"/>
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Gymshark</t>
+        </is>
+      </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>New GORE-TEX ePE Membrane</t>
+          <t>4.6 rating from 200 reviews</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
@@ -2019,7 +2015,7 @@
       <c r="A18" s="14" t="inlineStr"/>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>Rating 4.0 from 24 reviews</t>
+          <t>Free delivery on orders over $100</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
@@ -2030,7 +2026,7 @@
       <c r="A19" s="14" t="inlineStr"/>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>The Arc'teryx Guarantee</t>
+          <t>Pay in 4 Installments</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
@@ -2040,12 +2036,12 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Fabletics</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>$15 price point</t>
+          <t>25% Off Select Shoes</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
@@ -2056,7 +2052,7 @@
       <c r="A21" s="14" t="inlineStr"/>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>$19 swimsuits for new VIPs</t>
+          <t>Up to 30% Off Select Clothing and Accessories</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
@@ -2064,10 +2060,14 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="inlineStr"/>
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>50% off Jackets and Vests</t>
+          <t>Average delivery time 1-3 days</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
@@ -2078,7 +2078,7 @@
       <c r="A23" s="14" t="inlineStr"/>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>50% off Underscrubs</t>
+          <t>Most items returnable 60+ days</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
@@ -2089,7 +2089,7 @@
       <c r="A24" s="14" t="inlineStr"/>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>80% off everything</t>
+          <t>Rating 4.6 from 1,919 reviews</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
@@ -2100,7 +2100,7 @@
       <c r="A25" s="14" t="inlineStr"/>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>Breathable</t>
+          <t>Rating 4.7 from 6,660 reviews</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
@@ -2108,21 +2108,25 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="inlineStr"/>
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>Breathable, lightweight and wrinkle resistant</t>
+          <t>save up to 40%</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr"/>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>First Scrub Set for $15</t>
+          <t>30-day Returns</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
@@ -2133,7 +2137,7 @@
       <c r="A28" s="14" t="inlineStr"/>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>Lightweight</t>
+          <t>30-day returns</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
@@ -2144,7 +2148,7 @@
       <c r="A29" s="14" t="inlineStr"/>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>Wrinkle resistant</t>
+          <t>4.6 rating from 58 reviews</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
@@ -2154,23 +2158,23 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Gymshark</t>
+          <t>Patagonia</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>Free Returns</t>
+          <t>Guaranteed Quality</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr"/>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>4.6 rating from 200 reviews</t>
+          <t>Up to 40% Off</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
@@ -2178,10 +2182,14 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="14" t="inlineStr"/>
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Tracksmith</t>
+        </is>
+      </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>Free delivery on orders over $100</t>
+          <t>5.0 rating from 22 reviews</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
@@ -2192,7 +2200,7 @@
       <c r="A33" s="14" t="inlineStr"/>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>Pay in 4 Installments</t>
+          <t>Prices starting from $54.00</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
@@ -2200,10 +2208,14 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="14" t="inlineStr"/>
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Under Armour</t>
+        </is>
+      </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>Student Discount</t>
+          <t>1 to 5 days average delivery time</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
@@ -2211,14 +2223,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>New Balance</t>
-        </is>
-      </c>
+      <c r="A35" s="14" t="inlineStr"/>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>25% Off Select Shoes</t>
+          <t>25% Off BTS Gear</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
@@ -2229,7 +2237,7 @@
       <c r="A36" s="14" t="inlineStr"/>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>Up to 30% Off Select Clothing and Accessories</t>
+          <t>2X A Year</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
@@ -2237,14 +2245,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
+      <c r="A37" s="14" t="inlineStr"/>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>Average delivery time 1-3 days</t>
+          <t>30-50% Off Sitewide</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
@@ -2255,7 +2259,7 @@
       <c r="A38" s="14" t="inlineStr"/>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>Live Support Available</t>
+          <t>4.7 rating from 305 reviews</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
@@ -2266,7 +2270,7 @@
       <c r="A39" s="14" t="inlineStr"/>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>Most items returnable 60+ days</t>
+          <t>4.8 rating from 221 reviews</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
@@ -2277,7 +2281,7 @@
       <c r="A40" s="14" t="inlineStr"/>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>Rating 4.6 from 1,919 reviews</t>
+          <t>40% Off Winter Picks</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
@@ -2288,7 +2292,7 @@
       <c r="A41" s="14" t="inlineStr"/>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>Rating 4.7 from 6,660 reviews</t>
+          <t>50% Off</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
@@ -2296,25 +2300,21 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>On</t>
-        </is>
-      </c>
+      <c r="A42" s="14" t="inlineStr"/>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>save up to 40%</t>
+          <t>Rating 4.8 from 305 reviews</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="14" t="inlineStr"/>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>30-day Returns</t>
+          <t>Valid Jul 19 to Aug 21</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
@@ -2322,10 +2322,14 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="14" t="inlineStr"/>
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Vuori</t>
+        </is>
+      </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>30-day returns</t>
+          <t>100% Product Guarantee</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
@@ -2336,7 +2340,7 @@
       <c r="A45" s="14" t="inlineStr"/>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>4.6 rating from 58 reviews</t>
+          <t>120+ days returnable</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
@@ -2347,7 +2351,7 @@
       <c r="A46" s="14" t="inlineStr"/>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>Free Shipping</t>
+          <t>4-Way Stretch</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
@@ -2358,7 +2362,7 @@
       <c r="A47" s="14" t="inlineStr"/>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>Free shipping</t>
+          <t>4.6 rating from 14,413 reviews</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
@@ -2369,7 +2373,7 @@
       <c r="A48" s="14" t="inlineStr"/>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>More heel support</t>
+          <t>Free Shipping Over $75</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
@@ -2380,7 +2384,7 @@
       <c r="A49" s="14" t="inlineStr"/>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>New sockliner for easy step-in</t>
+          <t>Most items returnable 120+ days</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
@@ -2391,7 +2395,7 @@
       <c r="A50" s="14" t="inlineStr"/>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>Swiss-engineered</t>
+          <t>Rating 4.6 from 13,593 reviews</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
@@ -2399,10 +2403,14 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="14" t="inlineStr"/>
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>lululemon</t>
+        </is>
+      </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>Wider opening for better fit</t>
+          <t>25% Off Reduced Shop</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
@@ -2410,14 +2418,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>Patagonia</t>
-        </is>
-      </c>
+      <c r="A52" s="14" t="inlineStr"/>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>Guaranteed Quality</t>
+          <t>30+ days returnable</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">
@@ -2428,7 +2432,7 @@
       <c r="A53" s="14" t="inlineStr"/>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>Up to 40% Off</t>
+          <t>4.6 advertiser rating</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
@@ -2436,14 +2440,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>Tracksmith</t>
-        </is>
-      </c>
+      <c r="A54" s="14" t="inlineStr"/>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>5.0 rating from 22 reviews</t>
+          <t>4.6 rating from 104 reviews</t>
         </is>
       </c>
       <c r="C54" s="8" t="n">
@@ -2454,7 +2454,7 @@
       <c r="A55" s="14" t="inlineStr"/>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>Designed in Boston</t>
+          <t>4.7 rating from 183 reviews</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
@@ -2465,7 +2465,7 @@
       <c r="A56" s="14" t="inlineStr"/>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>Prices starting from $54.00</t>
+          <t>4.7 rating from 185 reviews</t>
         </is>
       </c>
       <c r="C56" s="8" t="n">
@@ -2473,377 +2473,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t>Under Armour</t>
-        </is>
-      </c>
+      <c r="A57" s="14" t="inlineStr"/>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>1 to 5 days average delivery time</t>
+          <t>Women's Gear Under $50</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="14" t="inlineStr"/>
-      <c r="B58" s="14" t="inlineStr">
-        <is>
-          <t>25% Off BTS Gear</t>
-        </is>
-      </c>
-      <c r="C58" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="14" t="inlineStr"/>
-      <c r="B59" s="14" t="inlineStr">
-        <is>
-          <t>2X A Year</t>
-        </is>
-      </c>
-      <c r="C59" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="14" t="inlineStr"/>
-      <c r="B60" s="14" t="inlineStr">
-        <is>
-          <t>30-50% Off Sitewide</t>
-        </is>
-      </c>
-      <c r="C60" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="14" t="inlineStr"/>
-      <c r="B61" s="14" t="inlineStr">
-        <is>
-          <t>4.7 rating from 305 reviews</t>
-        </is>
-      </c>
-      <c r="C61" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="14" t="inlineStr"/>
-      <c r="B62" s="14" t="inlineStr">
-        <is>
-          <t>4.8 rating from 221 reviews</t>
-        </is>
-      </c>
-      <c r="C62" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="14" t="inlineStr"/>
-      <c r="B63" s="14" t="inlineStr">
-        <is>
-          <t>40% Off Winter Picks</t>
-        </is>
-      </c>
-      <c r="C63" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="14" t="inlineStr"/>
-      <c r="B64" s="14" t="inlineStr">
-        <is>
-          <t>50% Off</t>
-        </is>
-      </c>
-      <c r="C64" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="14" t="inlineStr"/>
-      <c r="B65" s="14" t="inlineStr">
-        <is>
-          <t>Rating 4.8 from 305 reviews</t>
-        </is>
-      </c>
-      <c r="C65" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="14" t="inlineStr"/>
-      <c r="B66" s="14" t="inlineStr">
-        <is>
-          <t>Valid Jul 19 to Aug 21</t>
-        </is>
-      </c>
-      <c r="C66" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="7" t="inlineStr">
-        <is>
-          <t>Vuori</t>
-        </is>
-      </c>
-      <c r="B67" s="14" t="inlineStr">
-        <is>
-          <t>100% Product Guarantee</t>
-        </is>
-      </c>
-      <c r="C67" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="14" t="inlineStr"/>
-      <c r="B68" s="14" t="inlineStr">
-        <is>
-          <t>120+ days returnable</t>
-        </is>
-      </c>
-      <c r="C68" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="14" t="inlineStr"/>
-      <c r="B69" s="14" t="inlineStr">
-        <is>
-          <t>4-Way Stretch</t>
-        </is>
-      </c>
-      <c r="C69" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="14" t="inlineStr"/>
-      <c r="B70" s="14" t="inlineStr">
-        <is>
-          <t>4.6 rating from 14,413 reviews</t>
-        </is>
-      </c>
-      <c r="C70" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="14" t="inlineStr"/>
-      <c r="B71" s="14" t="inlineStr">
-        <is>
-          <t>Breathable</t>
-        </is>
-      </c>
-      <c r="C71" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="14" t="inlineStr"/>
-      <c r="B72" s="14" t="inlineStr">
-        <is>
-          <t>Free Shipping</t>
-        </is>
-      </c>
-      <c r="C72" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="14" t="inlineStr"/>
-      <c r="B73" s="14" t="inlineStr">
-        <is>
-          <t>Free Shipping Over $75</t>
-        </is>
-      </c>
-      <c r="C73" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="14" t="inlineStr"/>
-      <c r="B74" s="14" t="inlineStr">
-        <is>
-          <t>Lightweight and Breathable</t>
-        </is>
-      </c>
-      <c r="C74" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="14" t="inlineStr"/>
-      <c r="B75" s="14" t="inlineStr">
-        <is>
-          <t>Moisture Wicking</t>
-        </is>
-      </c>
-      <c r="C75" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="14" t="inlineStr"/>
-      <c r="B76" s="14" t="inlineStr">
-        <is>
-          <t>Most items returnable 120+ days</t>
-        </is>
-      </c>
-      <c r="C76" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="14" t="inlineStr"/>
-      <c r="B77" s="14" t="inlineStr">
-        <is>
-          <t>Rating 4.6 from 13,593 reviews</t>
-        </is>
-      </c>
-      <c r="C77" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="7" t="inlineStr">
-        <is>
-          <t>lululemon</t>
-        </is>
-      </c>
-      <c r="B78" s="14" t="inlineStr">
-        <is>
-          <t>25% Off Reduced Shop</t>
-        </is>
-      </c>
-      <c r="C78" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="14" t="inlineStr"/>
-      <c r="B79" s="14" t="inlineStr">
-        <is>
-          <t>30+ days returnable</t>
-        </is>
-      </c>
-      <c r="C79" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="14" t="inlineStr"/>
-      <c r="B80" s="14" t="inlineStr">
-        <is>
-          <t>4.6 advertiser rating</t>
-        </is>
-      </c>
-      <c r="C80" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="14" t="inlineStr"/>
-      <c r="B81" s="14" t="inlineStr">
-        <is>
-          <t>4.6 rating from 104 reviews</t>
-        </is>
-      </c>
-      <c r="C81" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="14" t="inlineStr"/>
-      <c r="B82" s="14" t="inlineStr">
-        <is>
-          <t>4.7 rating from 183 reviews</t>
-        </is>
-      </c>
-      <c r="C82" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="14" t="inlineStr"/>
-      <c r="B83" s="14" t="inlineStr">
-        <is>
-          <t>4.7 rating from 185 reviews</t>
-        </is>
-      </c>
-      <c r="C83" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="14" t="inlineStr"/>
-      <c r="B84" s="14" t="inlineStr">
-        <is>
-          <t>Anti-stink</t>
-        </is>
-      </c>
-      <c r="C84" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="14" t="inlineStr"/>
-      <c r="B85" s="14" t="inlineStr">
-        <is>
-          <t>Breathable</t>
-        </is>
-      </c>
-      <c r="C85" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="14" t="inlineStr"/>
-      <c r="B86" s="14" t="inlineStr">
-        <is>
-          <t>Dropping daily</t>
-        </is>
-      </c>
-      <c r="C86" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="14" t="inlineStr"/>
-      <c r="B87" s="14" t="inlineStr">
-        <is>
-          <t>Sweat-wicking</t>
-        </is>
-      </c>
-      <c r="C87" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="14" t="inlineStr"/>
-      <c r="B88" s="14" t="inlineStr">
-        <is>
-          <t>Thousands of gently used items</t>
-        </is>
-      </c>
-      <c r="C88" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="14" t="inlineStr"/>
-      <c r="B89" s="14" t="inlineStr">
-        <is>
-          <t>Women's Gear Under $50</t>
-        </is>
-      </c>
-      <c r="C89" s="8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2938,11 +2574,7 @@
           <t>Women, Runners, Yoga &amp; studio, Gym &amp; strength training, Everyday / athleisure</t>
         </is>
       </c>
-      <c r="F2" s="14" t="inlineStr">
-        <is>
-          <t>Sweat-wicking, Breathable, Anti-stink</t>
-        </is>
-      </c>
+      <c r="F2" s="14" t="inlineStr"/>
       <c r="G2" s="14" t="inlineStr">
         <is>
           <t>Search</t>
@@ -3048,7 +2680,7 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>Sustainability, Versatility / Gym-to-street</t>
+          <t>Sustainability, Versatility / Gym-to-street, Price / Value</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -3161,7 +2793,7 @@
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>Brand</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
@@ -3207,11 +2839,7 @@
           <t>Performance / Technical fabric, Versatility / Gym-to-street</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>Runners</t>
-        </is>
-      </c>
+      <c r="E9" s="14" t="inlineStr"/>
       <c r="F9" s="14" t="inlineStr"/>
       <c r="G9" s="14" t="inlineStr">
         <is>
@@ -3317,7 +2945,7 @@
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Brand</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr"/>
@@ -3356,7 +2984,7 @@
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>Performance / Technical fabric, Comfort / Feel, Style / Design, Versatility / Gym-to-street, Innovation / New technology</t>
+          <t>Performance / Technical fabric, Comfort / Feel, Style / Design, Versatility / Gym-to-street</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -3432,7 +3060,7 @@
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>Performance / Technical fabric, Style / Design, Versatility / Gym-to-street</t>
+          <t>Performance / Technical fabric, Style / Design, Versatility / Gym-to-street, Price / Value</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
@@ -3470,7 +3098,7 @@
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>Comfort / Feel</t>
+          <t>Comfort / Feel, Price / Value</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
@@ -3518,7 +3146,7 @@
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Free Shipping, 30-day Returns</t>
+          <t>30-day Returns</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -3631,7 +3259,7 @@
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>Everyday / athleisure, Gym &amp; strength training</t>
+          <t>Everyday / athleisure, Runners</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr"/>
@@ -3664,7 +3292,7 @@
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>Performance / Technical fabric, Comfort / Feel, Innovation / New technology, Style / Design</t>
+          <t>Performance / Technical fabric, Comfort / Feel, Innovation / New technology, Style / Design, Price / Value</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
@@ -3706,7 +3334,7 @@
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>Comfort / Feel, Performance / Technical fabric</t>
+          <t>Comfort / Feel, Performance / Technical fabric, Price / Value</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
@@ -3756,11 +3384,7 @@
           <t>Gym &amp; strength training, Runners, Everyday / athleisure</t>
         </is>
       </c>
-      <c r="F23" s="14" t="inlineStr">
-        <is>
-          <t>Free Returns</t>
-        </is>
-      </c>
+      <c r="F23" s="14" t="inlineStr"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
           <t>Search</t>
@@ -4102,7 +3726,7 @@
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>Versatility / Gym-to-street</t>
+          <t>Price / Value</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
@@ -4144,7 +3768,7 @@
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
-          <t>Performance / Technical fabric, Style / Design, Community / Belonging</t>
+          <t>Performance / Technical fabric, Style / Design</t>
         </is>
       </c>
       <c r="E33" s="14" t="inlineStr">
@@ -4186,7 +3810,7 @@
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>Performance / Technical fabric</t>
+          <t>Performance / Technical fabric, Price / Value</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
@@ -4196,7 +3820,7 @@
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>Designed in Boston, Prices starting from $54.00</t>
+          <t>Prices starting from $54.00</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
@@ -4228,7 +3852,7 @@
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
-          <t>Performance / Technical fabric, Comfort / Feel</t>
+          <t>Performance / Technical fabric, Comfort / Feel, Price / Value</t>
         </is>
       </c>
       <c r="E35" s="14" t="inlineStr">
@@ -4266,7 +3890,7 @@
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>Performance / Technical fabric</t>
+          <t>Performance / Technical fabric, Price / Value</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
@@ -4304,7 +3928,7 @@
       </c>
       <c r="D37" s="14" t="inlineStr">
         <is>
-          <t>Comfort / Feel, Style / Design, Versatility / Gym-to-street</t>
+          <t>Comfort / Feel, Style / Design, Versatility / Gym-to-street, Price / Value</t>
         </is>
       </c>
       <c r="E37" s="14" t="inlineStr">
@@ -4498,7 +4122,7 @@
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>Price / Value, Comfort / Feel, Sustainability</t>
+          <t>Price / Value, Comfort / Feel</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
@@ -4508,7 +4132,7 @@
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>First Scrub Set for $15, 50% off Underscrubs, 50% off Jackets and Vests, Breathable, lightweight and wrinkle resistant</t>
+          <t>First Scrub Set for $15, 50% off Underscrubs, 50% off Jackets and Vests</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
@@ -4632,11 +4256,7 @@
           <t>Everyday / athleisure</t>
         </is>
       </c>
-      <c r="F45" s="14" t="inlineStr">
-        <is>
-          <t>Thousands of gently used items, Dropping daily</t>
-        </is>
-      </c>
+      <c r="F45" s="14" t="inlineStr"/>
       <c r="G45" s="14" t="inlineStr">
         <is>
           <t>Search</t>
@@ -5020,7 +4640,7 @@
       </c>
       <c r="D55" s="14" t="inlineStr">
         <is>
-          <t>Comfort / Feel, Performance / Technical fabric</t>
+          <t>Comfort / Feel, Performance / Technical fabric, Price / Value</t>
         </is>
       </c>
       <c r="E55" s="14" t="inlineStr">
@@ -5217,11 +4837,7 @@
           <t>Performance / Technical fabric</t>
         </is>
       </c>
-      <c r="E60" s="14" t="inlineStr">
-        <is>
-          <t>Men, Gym &amp; strength training</t>
-        </is>
-      </c>
+      <c r="E60" s="14" t="inlineStr"/>
       <c r="F60" s="14" t="inlineStr"/>
       <c r="G60" s="14" t="inlineStr">
         <is>
@@ -5262,7 +4878,7 @@
       </c>
       <c r="F61" s="14" t="inlineStr">
         <is>
-          <t>Rating 4.6 from 1,919 reviews, Most items returnable 60+ days, Live Support Available</t>
+          <t>Rating 4.6 from 1,919 reviews, Most items returnable 60+ days</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
@@ -5294,7 +4910,7 @@
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>Performance / Technical fabric, Versatility / Gym-to-street, Comfort / Feel</t>
+          <t>Performance / Technical fabric, Versatility / Gym-to-street, Comfort / Feel, Price / Value</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
@@ -5304,7 +4920,7 @@
       </c>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>4-Way Stretch, Moisture Wicking, Breathable, 100% Product Guarantee, Free Shipping Over $75, Rating 4.6 from 13,593 reviews, Most items returnable 120+ days</t>
+          <t>4-Way Stretch, 100% Product Guarantee, Free Shipping Over $75, Rating 4.6 from 13,593 reviews, Most items returnable 120+ days</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
@@ -5336,7 +4952,7 @@
       </c>
       <c r="D63" s="14" t="inlineStr">
         <is>
-          <t>Performance / Technical fabric, Style / Design, Versatility / Gym-to-street</t>
+          <t>Performance / Technical fabric, Style / Design, Versatility / Gym-to-street, Price / Value</t>
         </is>
       </c>
       <c r="E63" s="14" t="inlineStr">
@@ -5416,7 +5032,7 @@
       </c>
       <c r="D65" s="14" t="inlineStr">
         <is>
-          <t>Comfort / Feel, Versatility / Gym-to-street, Style / Design, Innovation / New technology</t>
+          <t>Comfort / Feel, Versatility / Gym-to-street, Style / Design, Innovation / New technology, Price / Value</t>
         </is>
       </c>
       <c r="E65" s="14" t="inlineStr">
@@ -5462,11 +5078,7 @@
           <t>Women, Men, Everyday / athleisure</t>
         </is>
       </c>
-      <c r="F66" s="14" t="inlineStr">
-        <is>
-          <t>Free Shipping, Lightweight and Breathable</t>
-        </is>
-      </c>
+      <c r="F66" s="14" t="inlineStr"/>
       <c r="G66" s="14" t="inlineStr">
         <is>
           <t>Search</t>
@@ -5529,12 +5141,12 @@
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Brand</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>Innovation / New technology</t>
+          <t>Community / Belonging</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
@@ -5567,12 +5179,12 @@
       </c>
       <c r="C69" s="14" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Brand</t>
         </is>
       </c>
       <c r="D69" s="14" t="inlineStr">
         <is>
-          <t>Performance / Technical fabric, Versatility / Gym-to-street</t>
+          <t>Performance / Technical fabric, Versatility / Gym-to-street, Community / Belonging, Price / Value</t>
         </is>
       </c>
       <c r="E69" s="14" t="inlineStr">
@@ -5724,7 +5336,7 @@
       </c>
       <c r="D73" s="14" t="inlineStr">
         <is>
-          <t>Performance / Technical fabric, Comfort / Feel, Community / Belonging</t>
+          <t>Performance / Technical fabric, Comfort / Feel, Community / Belonging, Price / Value</t>
         </is>
       </c>
       <c r="E73" s="14" t="inlineStr">
@@ -5772,7 +5384,7 @@
       </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>Free delivery on orders over $100, Free Returns, 4.6 rating from 200 reviews, Pay in 4 Installments, Student Discount</t>
+          <t>Free delivery on orders over $100, 4.6 rating from 200 reviews, Pay in 4 Installments</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
@@ -5890,7 +5502,7 @@
       </c>
       <c r="F77" s="14" t="inlineStr">
         <is>
-          <t>4.6 rating from 58 reviews, 30-day returns, Free shipping, New sockliner for easy step-in, Wider opening for better fit, More heel support</t>
+          <t>4.6 rating from 58 reviews, 30-day returns</t>
         </is>
       </c>
       <c r="G77" s="14" t="inlineStr">
@@ -5960,7 +5572,7 @@
       </c>
       <c r="D79" s="14" t="inlineStr">
         <is>
-          <t>Performance / Technical fabric, Comfort / Feel, Versatility / Gym-to-street, Innovation / New technology, Style / Design, Price / Value, Sustainability</t>
+          <t>Performance / Technical fabric, Comfort / Feel, Versatility / Gym-to-street, Innovation / New technology, Price / Value</t>
         </is>
       </c>
       <c r="E79" s="14" t="inlineStr">
@@ -5970,7 +5582,7 @@
       </c>
       <c r="F79" s="14" t="inlineStr">
         <is>
-          <t>Swiss-engineered, save up to 40%</t>
+          <t>save up to 40%</t>
         </is>
       </c>
       <c r="G79" s="14" t="inlineStr">
@@ -6078,7 +5690,7 @@
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>Performance / Technical fabric, Innovation / New technology</t>
+          <t>Performance / Technical fabric, Innovation / New technology, Price / Value</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
@@ -6158,7 +5770,7 @@
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>Style / Design, Versatility / Gym-to-street, Community / Belonging</t>
+          <t>Style / Design, Versatility / Gym-to-street</t>
         </is>
       </c>
       <c r="E84" s="14" t="inlineStr">
@@ -6168,7 +5780,7 @@
       </c>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>4.5 rating from 21,615 reviews, Order accuracy 95 to 100%, Celeb-approved</t>
+          <t>4.5 rating from 21,615 reviews, Order accuracy 95 to 100%</t>
         </is>
       </c>
       <c r="G84" s="14" t="inlineStr">
@@ -6200,7 +5812,7 @@
       </c>
       <c r="D85" s="14" t="inlineStr">
         <is>
-          <t>Style / Design, Versatility / Gym-to-street</t>
+          <t>Style / Design, Versatility / Gym-to-street, Community / Belonging</t>
         </is>
       </c>
       <c r="E85" s="14" t="inlineStr">
@@ -6246,11 +5858,7 @@
           <t>Women, Yoga &amp; studio, Everyday / athleisure</t>
         </is>
       </c>
-      <c r="F86" s="14" t="inlineStr">
-        <is>
-          <t>Performance-Engineered, Yogi-Tested, Free Worldwide Shipping</t>
-        </is>
-      </c>
+      <c r="F86" s="14" t="inlineStr"/>
       <c r="G86" s="14" t="inlineStr">
         <is>
           <t>Search</t>
@@ -6328,7 +5936,7 @@
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>Rating 4.5 from 21,615 reviews, Free Shipping and Free Returns, Average delivery time 1 to 4 days</t>
+          <t>Rating 4.5 from 21,615 reviews, Average delivery time 1 to 4 days</t>
         </is>
       </c>
       <c r="G88" s="14" t="inlineStr">
@@ -6358,7 +5966,11 @@
           <t>Promotional</t>
         </is>
       </c>
-      <c r="D89" s="14" t="inlineStr"/>
+      <c r="D89" s="14" t="inlineStr">
+        <is>
+          <t>Price / Value</t>
+        </is>
+      </c>
       <c r="E89" s="14" t="inlineStr">
         <is>
           <t>Everyday / athleisure</t>
@@ -6398,7 +6010,7 @@
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>Performance / Technical fabric, Versatility / Gym-to-street, Style / Design</t>
+          <t>Performance / Technical fabric, Versatility / Gym-to-street, Style / Design, Price / Value</t>
         </is>
       </c>
       <c r="E90" s="14" t="inlineStr">
@@ -6634,12 +6246,12 @@
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>Performance / Technical fabric, Versatility / Gym-to-street</t>
+          <t>Performance / Technical fabric</t>
         </is>
       </c>
       <c r="E96" s="14" t="inlineStr">
         <is>
-          <t>Outdoor &amp; hiking, Runners</t>
+          <t>Outdoor &amp; hiking</t>
         </is>
       </c>
       <c r="F96" s="14" t="inlineStr"/>
@@ -6680,11 +6292,7 @@
           <t>Men, Outdoor &amp; hiking</t>
         </is>
       </c>
-      <c r="F97" s="14" t="inlineStr">
-        <is>
-          <t>Gore-tex Jackets, Insulated Jackets, New GORE-TEX ePE Membrane</t>
-        </is>
-      </c>
+      <c r="F97" s="14" t="inlineStr"/>
       <c r="G97" s="14" t="inlineStr">
         <is>
           <t>Search</t>
@@ -6838,7 +6446,7 @@
       </c>
       <c r="F101" s="14" t="inlineStr">
         <is>
-          <t>Free Shipping and Returns, The Arc'teryx Guarantee</t>
+          <t>The Arc'teryx Guarantee</t>
         </is>
       </c>
       <c r="G101" s="14" t="inlineStr">
@@ -6880,7 +6488,7 @@
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>Breathable, Lightweight, Wrinkle resistant, $15 price point</t>
+          <t>$15 price point</t>
         </is>
       </c>
       <c r="G102" s="14" t="inlineStr">
